--- a/task165/golden/salt_commitment_2026-27.xlsx
+++ b/task165/golden/salt_commitment_2026-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="454">
   <si>
     <t>Commit 2,200 t of rock salt above the rolled-over 39,100 t for November 2026 to March 2027</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Seasonal tonnage to commit (t, nearest 100)</t>
   </si>
   <si>
-    <t>Gain line from the 202 collectors moved to Priority 1 from 1 November 2022 to 1 November 2025 (392.1 lane-km), each street's salt per lane-km per WSI point after its move less before, against before, weighted by lane-km</t>
+    <t>Gain line from the 431 collectors moved to Priority 1 from 1 November 2022 to 1 November 2025 (875.4 lane-km), each street's salt per lane-km per WSI point after its move less before, against before, weighted by lane-km</t>
   </si>
   <si>
     <t>Gain at no Priority 2 salt, planning-severity winter (t per lane-km)</t>
@@ -92,1212 +92,1248 @@
     <t>Gain, planning winter (t)</t>
   </si>
   <si>
-    <t>RS189095</t>
-  </si>
-  <si>
-    <t>Applewood Way</t>
+    <t>RS208377</t>
+  </si>
+  <si>
+    <t>Beckett Street</t>
+  </si>
+  <si>
+    <t>Prospect Avenue</t>
+  </si>
+  <si>
+    <t>Locke Street</t>
+  </si>
+  <si>
+    <t>KLV</t>
+  </si>
+  <si>
+    <t>RS208388</t>
+  </si>
+  <si>
+    <t>Norfolk Boulevard South</t>
+  </si>
+  <si>
+    <t>RS208484</t>
+  </si>
+  <si>
+    <t>Falcon Boulevard</t>
+  </si>
+  <si>
+    <t>RS208747</t>
+  </si>
+  <si>
+    <t>Beacon Avenue</t>
+  </si>
+  <si>
+    <t>RS208774</t>
+  </si>
+  <si>
+    <t>McCormick Avenue</t>
+  </si>
+  <si>
+    <t>RS208837</t>
+  </si>
+  <si>
+    <t>Fleming Road South</t>
+  </si>
+  <si>
+    <t>RS199918</t>
+  </si>
+  <si>
+    <t>Blair Road</t>
+  </si>
+  <si>
+    <t>Deerfield Drive</t>
+  </si>
+  <si>
+    <t>Monarch Street</t>
+  </si>
+  <si>
+    <t>RS200045</t>
+  </si>
+  <si>
+    <t>Merritt Avenue</t>
+  </si>
+  <si>
+    <t>RS200247</t>
+  </si>
+  <si>
+    <t>Fenwick Drive North</t>
+  </si>
+  <si>
+    <t>RS200333</t>
+  </si>
+  <si>
+    <t>York Avenue</t>
+  </si>
+  <si>
+    <t>RS200346</t>
+  </si>
+  <si>
+    <t>Union Line</t>
+  </si>
+  <si>
+    <t>RS200478</t>
+  </si>
+  <si>
+    <t>Spruce Boulevard</t>
+  </si>
+  <si>
+    <t>RS200547</t>
+  </si>
+  <si>
+    <t>RS205218</t>
+  </si>
+  <si>
+    <t>Bruce Street</t>
+  </si>
+  <si>
+    <t>Victoria Park Drive East</t>
+  </si>
+  <si>
+    <t>Maplewood Boulevard East</t>
+  </si>
+  <si>
+    <t>RS205236</t>
+  </si>
+  <si>
+    <t>Lambton Crescent</t>
+  </si>
+  <si>
+    <t>RS205320</t>
+  </si>
+  <si>
+    <t>Lawrence Road</t>
+  </si>
+  <si>
+    <t>RS205325</t>
+  </si>
+  <si>
+    <t>Cairns Drive</t>
+  </si>
+  <si>
+    <t>RS205338</t>
+  </si>
+  <si>
+    <t>Tudor Street</t>
+  </si>
+  <si>
+    <t>RS205394</t>
+  </si>
+  <si>
+    <t>Balsam Avenue South</t>
+  </si>
+  <si>
+    <t>RS212002</t>
+  </si>
+  <si>
+    <t>Carlton Street</t>
+  </si>
+  <si>
+    <t>Keegan Street</t>
+  </si>
+  <si>
+    <t>Raglan Crescent</t>
+  </si>
+  <si>
+    <t>RS212004</t>
   </si>
   <si>
     <t>Heather Way</t>
   </si>
   <si>
+    <t>RS212007</t>
+  </si>
+  <si>
+    <t>Inglewood Drive South</t>
+  </si>
+  <si>
+    <t>RS212073</t>
+  </si>
+  <si>
+    <t>O'Connor Crescent</t>
+  </si>
+  <si>
+    <t>RS212200</t>
+  </si>
+  <si>
+    <t>Oxford Line</t>
+  </si>
+  <si>
+    <t>RS212301</t>
+  </si>
+  <si>
+    <t>Keats Avenue North</t>
+  </si>
+  <si>
+    <t>RS204744</t>
+  </si>
+  <si>
+    <t>Elliot Boulevard</t>
+  </si>
+  <si>
+    <t>Dunbar Boulevard</t>
+  </si>
+  <si>
+    <t>RS204769</t>
+  </si>
+  <si>
+    <t>Elmwood Avenue</t>
+  </si>
+  <si>
+    <t>RS205055</t>
+  </si>
+  <si>
+    <t>RS205188</t>
+  </si>
+  <si>
+    <t>Sydenham Street</t>
+  </si>
+  <si>
+    <t>RS205208</t>
+  </si>
+  <si>
+    <t>Vance Boulevard</t>
+  </si>
+  <si>
+    <t>RS205213</t>
+  </si>
+  <si>
+    <t>Kensington Way West</t>
+  </si>
+  <si>
+    <t>RS208953</t>
+  </si>
+  <si>
+    <t>Foxwood Avenue</t>
+  </si>
+  <si>
+    <t>Spencer Boulevard</t>
+  </si>
+  <si>
+    <t>Hunter Road</t>
+  </si>
+  <si>
+    <t>RS209098</t>
+  </si>
+  <si>
+    <t>Brock Road East</t>
+  </si>
+  <si>
+    <t>RS209107</t>
+  </si>
+  <si>
+    <t>RS209109</t>
+  </si>
+  <si>
+    <t>Franklin Drive North</t>
+  </si>
+  <si>
+    <t>RS209146</t>
+  </si>
+  <si>
+    <t>Pembroke Way</t>
+  </si>
+  <si>
+    <t>RS209369</t>
+  </si>
+  <si>
+    <t>RS210247</t>
+  </si>
+  <si>
+    <t>Granville Avenue</t>
+  </si>
+  <si>
+    <t>Kerr Street West</t>
+  </si>
+  <si>
+    <t>Finch Avenue South</t>
+  </si>
+  <si>
+    <t>RS210248</t>
+  </si>
+  <si>
+    <t>Park Lawn Street</t>
+  </si>
+  <si>
+    <t>RS210259</t>
+  </si>
+  <si>
+    <t>Howard Avenue</t>
+  </si>
+  <si>
+    <t>RS210281</t>
+  </si>
+  <si>
+    <t>Hagen Way</t>
+  </si>
+  <si>
+    <t>RS210361</t>
+  </si>
+  <si>
+    <t>Dalhousie Street East</t>
+  </si>
+  <si>
+    <t>RS210561</t>
+  </si>
+  <si>
+    <t>Yorkshire Road</t>
+  </si>
+  <si>
+    <t>RS203270</t>
+  </si>
+  <si>
+    <t>Oakdale Line</t>
+  </si>
+  <si>
+    <t>Nash Street</t>
+  </si>
+  <si>
+    <t>Briar Street</t>
+  </si>
+  <si>
+    <t>RS203588</t>
+  </si>
+  <si>
+    <t>Radcliffe Road</t>
+  </si>
+  <si>
+    <t>RS203787</t>
+  </si>
+  <si>
+    <t>Wilson Avenue North</t>
+  </si>
+  <si>
+    <t>RS203835</t>
+  </si>
+  <si>
+    <t>Cornwall Avenue</t>
+  </si>
+  <si>
+    <t>RS203949</t>
+  </si>
+  <si>
+    <t>Lorne Avenue</t>
+  </si>
+  <si>
+    <t>RS203993</t>
+  </si>
+  <si>
+    <t>York Way South</t>
+  </si>
+  <si>
+    <t>RS199363</t>
+  </si>
+  <si>
+    <t>Seneca Street</t>
+  </si>
+  <si>
+    <t>RS199415</t>
+  </si>
+  <si>
+    <t>Harding Avenue</t>
+  </si>
+  <si>
+    <t>RS199496</t>
+  </si>
+  <si>
+    <t>Bolton Street</t>
+  </si>
+  <si>
+    <t>RS199811</t>
+  </si>
+  <si>
+    <t>Reid Road</t>
+  </si>
+  <si>
+    <t>RS199818</t>
+  </si>
+  <si>
+    <t>Doherty Street West</t>
+  </si>
+  <si>
+    <t>RS199886</t>
+  </si>
+  <si>
+    <t>Halton Line East</t>
+  </si>
+  <si>
+    <t>RS199894</t>
+  </si>
+  <si>
+    <t>Delaware Way</t>
+  </si>
+  <si>
+    <t>RS208011</t>
+  </si>
+  <si>
+    <t>Ashby Boulevard</t>
+  </si>
+  <si>
+    <t>Chalmers Road</t>
+  </si>
+  <si>
+    <t>LKS</t>
+  </si>
+  <si>
+    <t>RS208012</t>
+  </si>
+  <si>
+    <t>RS208246</t>
+  </si>
+  <si>
+    <t>Cotswold Boulevard</t>
+  </si>
+  <si>
+    <t>RS208269</t>
+  </si>
+  <si>
+    <t>Riverside Way</t>
+  </si>
+  <si>
+    <t>RS208342</t>
+  </si>
+  <si>
+    <t>Keegan Street East</t>
+  </si>
+  <si>
+    <t>RS208344</t>
+  </si>
+  <si>
     <t>Greenbank Line</t>
   </si>
   <si>
-    <t>KLV</t>
-  </si>
-  <si>
-    <t>RS189444</t>
-  </si>
-  <si>
-    <t>Hastings Road</t>
-  </si>
-  <si>
-    <t>RS189504</t>
-  </si>
-  <si>
-    <t>Hazel Crescent</t>
-  </si>
-  <si>
-    <t>RS189524</t>
-  </si>
-  <si>
-    <t>Everett Road</t>
-  </si>
-  <si>
-    <t>RS189534</t>
-  </si>
-  <si>
-    <t>Nash Street</t>
-  </si>
-  <si>
-    <t>RS189633</t>
-  </si>
-  <si>
-    <t>Spruce Boulevard</t>
-  </si>
-  <si>
-    <t>RS188037</t>
-  </si>
-  <si>
-    <t>Colborne Avenue</t>
-  </si>
-  <si>
-    <t>Sunnyside Avenue</t>
-  </si>
-  <si>
-    <t>Garfield Crescent</t>
-  </si>
-  <si>
-    <t>RS188056</t>
-  </si>
-  <si>
-    <t>Oxford Line</t>
-  </si>
-  <si>
-    <t>RS188073</t>
-  </si>
-  <si>
-    <t>Bayview Street</t>
-  </si>
-  <si>
-    <t>RS188102</t>
-  </si>
-  <si>
-    <t>Camden Boulevard</t>
-  </si>
-  <si>
-    <t>RS188244</t>
-  </si>
-  <si>
-    <t>Nelson Avenue</t>
-  </si>
-  <si>
-    <t>RS188422</t>
+    <t>RS200692</t>
+  </si>
+  <si>
+    <t>Clarence Avenue</t>
+  </si>
+  <si>
+    <t>Chalmers Road South</t>
+  </si>
+  <si>
+    <t>Tiffany Street West</t>
+  </si>
+  <si>
+    <t>RS200759</t>
+  </si>
+  <si>
+    <t>Regent Line West</t>
+  </si>
+  <si>
+    <t>RS200815</t>
+  </si>
+  <si>
+    <t>Coronation Street</t>
+  </si>
+  <si>
+    <t>RS200837</t>
+  </si>
+  <si>
+    <t>Vaughan Crescent</t>
+  </si>
+  <si>
+    <t>RS200995</t>
+  </si>
+  <si>
+    <t>RS201013</t>
+  </si>
+  <si>
+    <t>RS201046</t>
+  </si>
+  <si>
+    <t>Bridgeport Crescent</t>
+  </si>
+  <si>
+    <t>RS209395</t>
+  </si>
+  <si>
+    <t>Dorchester Drive</t>
+  </si>
+  <si>
+    <t>Willow Avenue</t>
+  </si>
+  <si>
+    <t>RS209470</t>
+  </si>
+  <si>
+    <t>Burnside Line</t>
+  </si>
+  <si>
+    <t>RS209601</t>
+  </si>
+  <si>
+    <t>Rosedale Drive West</t>
+  </si>
+  <si>
+    <t>RS209692</t>
+  </si>
+  <si>
+    <t>Fairfield Boulevard</t>
+  </si>
+  <si>
+    <t>RS210012</t>
+  </si>
+  <si>
+    <t>Scarlett Road</t>
+  </si>
+  <si>
+    <t>RS210159</t>
+  </si>
+  <si>
+    <t>RS197618</t>
+  </si>
+  <si>
+    <t>Osler Street</t>
+  </si>
+  <si>
+    <t>Essex Avenue</t>
+  </si>
+  <si>
+    <t>RS197827</t>
+  </si>
+  <si>
+    <t>RS198014</t>
+  </si>
+  <si>
+    <t>Rutherford Drive North</t>
+  </si>
+  <si>
+    <t>RS198045</t>
+  </si>
+  <si>
+    <t>Orchard Boulevard</t>
+  </si>
+  <si>
+    <t>RS198152</t>
+  </si>
+  <si>
+    <t>Heritage Way South</t>
+  </si>
+  <si>
+    <t>RS198167</t>
+  </si>
+  <si>
+    <t>Stratford Avenue</t>
+  </si>
+  <si>
+    <t>RS198214</t>
+  </si>
+  <si>
+    <t>RS202758</t>
+  </si>
+  <si>
+    <t>Russell Road</t>
+  </si>
+  <si>
+    <t>Allan Way</t>
+  </si>
+  <si>
+    <t>RS202838</t>
+  </si>
+  <si>
+    <t>Canterbury Street North</t>
+  </si>
+  <si>
+    <t>RS202871</t>
+  </si>
+  <si>
+    <t>Mackenzie Street</t>
+  </si>
+  <si>
+    <t>RS202939</t>
+  </si>
+  <si>
+    <t>Eastwood Line</t>
+  </si>
+  <si>
+    <t>RS203040</t>
+  </si>
+  <si>
+    <t>Kent Way</t>
+  </si>
+  <si>
+    <t>RS203249</t>
+  </si>
+  <si>
+    <t>Hickory Drive</t>
+  </si>
+  <si>
+    <t>RS196428</t>
+  </si>
+  <si>
+    <t>Pleasant Avenue</t>
+  </si>
+  <si>
+    <t>Osler Avenue South</t>
+  </si>
+  <si>
+    <t>Lambton Line West</t>
+  </si>
+  <si>
+    <t>RS196471</t>
+  </si>
+  <si>
+    <t>Balsam Road</t>
+  </si>
+  <si>
+    <t>RS196557</t>
+  </si>
+  <si>
+    <t>Leeds Avenue</t>
+  </si>
+  <si>
+    <t>RS196602</t>
+  </si>
+  <si>
+    <t>Cobden Avenue</t>
+  </si>
+  <si>
+    <t>RS196635</t>
+  </si>
+  <si>
+    <t>Tobin Way North</t>
+  </si>
+  <si>
+    <t>RS196697</t>
+  </si>
+  <si>
+    <t>Hawthorne Line South</t>
+  </si>
+  <si>
+    <t>RS196938</t>
+  </si>
+  <si>
+    <t>Mohawk Street</t>
+  </si>
+  <si>
+    <t>RS201469</t>
   </si>
   <si>
     <t>Shaftesbury Drive</t>
   </si>
   <si>
-    <t>RS186849</t>
-  </si>
-  <si>
-    <t>Hagen Way</t>
-  </si>
-  <si>
-    <t>Alderson Boulevard</t>
-  </si>
-  <si>
-    <t>Fleming Street</t>
-  </si>
-  <si>
-    <t>RS186853</t>
-  </si>
-  <si>
-    <t>Blair Road</t>
-  </si>
-  <si>
-    <t>RS186867</t>
+    <t>Milford Way</t>
+  </si>
+  <si>
+    <t>RS201489</t>
+  </si>
+  <si>
+    <t>Cumberland Road South</t>
+  </si>
+  <si>
+    <t>RS201549</t>
+  </si>
+  <si>
+    <t>Mayfair Drive</t>
+  </si>
+  <si>
+    <t>RS201555</t>
+  </si>
+  <si>
+    <t>Parkside Crescent</t>
+  </si>
+  <si>
+    <t>RS201724</t>
+  </si>
+  <si>
+    <t>Lawrence Way West</t>
+  </si>
+  <si>
+    <t>RS201767</t>
+  </si>
+  <si>
+    <t>Eglinton Drive East</t>
+  </si>
+  <si>
+    <t>RS201858</t>
+  </si>
+  <si>
+    <t>Lockhart Drive</t>
+  </si>
+  <si>
+    <t>RS204342</t>
+  </si>
+  <si>
+    <t>Somerset Avenue</t>
+  </si>
+  <si>
+    <t>Auburn Crescent</t>
+  </si>
+  <si>
+    <t>Southgate Street</t>
+  </si>
+  <si>
+    <t>RS204454</t>
+  </si>
+  <si>
+    <t>Millbrook Drive West</t>
+  </si>
+  <si>
+    <t>RS204507</t>
+  </si>
+  <si>
+    <t>RS204580</t>
+  </si>
+  <si>
+    <t>RS204688</t>
+  </si>
+  <si>
+    <t>RS204705</t>
+  </si>
+  <si>
+    <t>Douglas Way North</t>
+  </si>
+  <si>
+    <t>RS201978</t>
+  </si>
+  <si>
+    <t>Hillcrest Avenue</t>
+  </si>
+  <si>
+    <t>MPF</t>
+  </si>
+  <si>
+    <t>RS201980</t>
+  </si>
+  <si>
+    <t>Walnut Avenue</t>
+  </si>
+  <si>
+    <t>RS202176</t>
+  </si>
+  <si>
+    <t>RS202213</t>
+  </si>
+  <si>
+    <t>Hollis Boulevard</t>
+  </si>
+  <si>
+    <t>RS202295</t>
+  </si>
+  <si>
+    <t>Rutherford Boulevard</t>
+  </si>
+  <si>
+    <t>RS202364</t>
+  </si>
+  <si>
+    <t>Valleyview Drive</t>
+  </si>
+  <si>
+    <t>RS202380</t>
+  </si>
+  <si>
+    <t>RS207346</t>
+  </si>
+  <si>
+    <t>Holland Crescent</t>
+  </si>
+  <si>
+    <t>Inglewood Avenue</t>
+  </si>
+  <si>
+    <t>O'Connor Boulevard East</t>
+  </si>
+  <si>
+    <t>RS207397</t>
+  </si>
+  <si>
+    <t>RS207466</t>
+  </si>
+  <si>
+    <t>Irving Avenue</t>
+  </si>
+  <si>
+    <t>RS207564</t>
+  </si>
+  <si>
+    <t>RS207747</t>
+  </si>
+  <si>
+    <t>Barclay Avenue</t>
+  </si>
+  <si>
+    <t>RS207749</t>
+  </si>
+  <si>
+    <t>Pritchard Avenue</t>
+  </si>
+  <si>
+    <t>RS197026</t>
+  </si>
+  <si>
+    <t>Gardner Boulevard</t>
+  </si>
+  <si>
+    <t>Minto Crescent</t>
+  </si>
+  <si>
+    <t>RS197110</t>
+  </si>
+  <si>
+    <t>Woodbine Avenue</t>
+  </si>
+  <si>
+    <t>RS197193</t>
+  </si>
+  <si>
+    <t>Simcoe Boulevard</t>
+  </si>
+  <si>
+    <t>RS197196</t>
+  </si>
+  <si>
+    <t>RS197380</t>
+  </si>
+  <si>
+    <t>RS197538</t>
+  </si>
+  <si>
+    <t>Maplewood Avenue</t>
+  </si>
+  <si>
+    <t>RS197608</t>
+  </si>
+  <si>
+    <t>RS198858</t>
+  </si>
+  <si>
+    <t>RS199131</t>
+  </si>
+  <si>
+    <t>RS199175</t>
+  </si>
+  <si>
+    <t>Grafton Avenue</t>
+  </si>
+  <si>
+    <t>RS199227</t>
+  </si>
+  <si>
+    <t>Norwood Way</t>
+  </si>
+  <si>
+    <t>RS199255</t>
+  </si>
+  <si>
+    <t>RS199311</t>
+  </si>
+  <si>
+    <t>Trafalgar Boulevard</t>
+  </si>
+  <si>
+    <t>RS199344</t>
+  </si>
+  <si>
+    <t>RS213681</t>
+  </si>
+  <si>
+    <t>Rideau Avenue</t>
+  </si>
+  <si>
+    <t>Ardagh Road</t>
+  </si>
+  <si>
+    <t>RS213706</t>
+  </si>
+  <si>
+    <t>RS213746</t>
+  </si>
+  <si>
+    <t>Waterloo Road</t>
+  </si>
+  <si>
+    <t>RS213905</t>
+  </si>
+  <si>
+    <t>Wilson Street</t>
+  </si>
+  <si>
+    <t>RS213985</t>
+  </si>
+  <si>
+    <t>RS214001</t>
+  </si>
+  <si>
+    <t>RS211172</t>
   </si>
   <si>
     <t>Selkirk Avenue</t>
   </si>
   <si>
-    <t>RS186989</t>
-  </si>
-  <si>
-    <t>Birch Crescent</t>
-  </si>
-  <si>
-    <t>RS187112</t>
-  </si>
-  <si>
-    <t>York Avenue</t>
-  </si>
-  <si>
-    <t>RS187269</t>
-  </si>
-  <si>
-    <t>Bolton Street</t>
-  </si>
-  <si>
-    <t>RS187315</t>
-  </si>
-  <si>
-    <t>Hunter Road</t>
-  </si>
-  <si>
-    <t>RS180348</t>
-  </si>
-  <si>
-    <t>Harding Avenue</t>
-  </si>
-  <si>
-    <t>Livingston Road</t>
-  </si>
-  <si>
-    <t>Union Line</t>
-  </si>
-  <si>
-    <t>RS180438</t>
-  </si>
-  <si>
-    <t>Seneca Street</t>
-  </si>
-  <si>
-    <t>RS180477</t>
-  </si>
-  <si>
-    <t>Avonlea Line</t>
-  </si>
-  <si>
-    <t>RS180490</t>
-  </si>
-  <si>
-    <t>Tamarack Boulevard</t>
-  </si>
-  <si>
-    <t>RS180531</t>
-  </si>
-  <si>
-    <t>Grafton Avenue</t>
-  </si>
-  <si>
-    <t>RS180651</t>
-  </si>
-  <si>
-    <t>Quarry Way</t>
-  </si>
-  <si>
-    <t>RS180825</t>
+    <t>Winston Way</t>
+  </si>
+  <si>
+    <t>RS211303</t>
+  </si>
+  <si>
+    <t>Juniper Road</t>
+  </si>
+  <si>
+    <t>RS211321</t>
+  </si>
+  <si>
+    <t>RS211344</t>
+  </si>
+  <si>
+    <t>RS211799</t>
+  </si>
+  <si>
+    <t>RS211900</t>
+  </si>
+  <si>
+    <t>Trillium Drive</t>
+  </si>
+  <si>
+    <t>RS212371</t>
+  </si>
+  <si>
+    <t>Sherwood Way</t>
+  </si>
+  <si>
+    <t>Chester Drive</t>
+  </si>
+  <si>
+    <t>RS212555</t>
+  </si>
+  <si>
+    <t>Knox Road East</t>
+  </si>
+  <si>
+    <t>RS212623</t>
+  </si>
+  <si>
+    <t>Sinclair Boulevard</t>
+  </si>
+  <si>
+    <t>RS212634</t>
+  </si>
+  <si>
+    <t>RS212656</t>
+  </si>
+  <si>
+    <t>Kipling Road</t>
+  </si>
+  <si>
+    <t>RS212758</t>
+  </si>
+  <si>
+    <t>RS210721</t>
+  </si>
+  <si>
+    <t>Halton Line</t>
+  </si>
+  <si>
+    <t>Morris Crescent</t>
+  </si>
+  <si>
+    <t>RS210885</t>
+  </si>
+  <si>
+    <t>RS210907</t>
+  </si>
+  <si>
+    <t>Edison Street</t>
+  </si>
+  <si>
+    <t>RS210937</t>
+  </si>
+  <si>
+    <t>RS211093</t>
+  </si>
+  <si>
+    <t>Cumberland Avenue</t>
+  </si>
+  <si>
+    <t>RS211094</t>
+  </si>
+  <si>
+    <t>Grafton Street South</t>
+  </si>
+  <si>
+    <t>RS206825</t>
+  </si>
+  <si>
+    <t>Blackburn Street</t>
+  </si>
+  <si>
+    <t>Grey Way</t>
+  </si>
+  <si>
+    <t>RDG</t>
+  </si>
+  <si>
+    <t>RS206833</t>
+  </si>
+  <si>
+    <t>Quinlan Drive</t>
+  </si>
+  <si>
+    <t>RS206912</t>
+  </si>
+  <si>
+    <t>RS207002</t>
+  </si>
+  <si>
+    <t>RS207129</t>
+  </si>
+  <si>
+    <t>RS207241</t>
+  </si>
+  <si>
+    <t>RS202437</t>
+  </si>
+  <si>
+    <t>Cambrian Boulevard</t>
+  </si>
+  <si>
+    <t>Stafford Avenue East</t>
+  </si>
+  <si>
+    <t>RS202484</t>
+  </si>
+  <si>
+    <t>Woodlawn Line</t>
+  </si>
+  <si>
+    <t>RS202526</t>
+  </si>
+  <si>
+    <t>RS202597</t>
+  </si>
+  <si>
+    <t>Simcoe Way South</t>
+  </si>
+  <si>
+    <t>RS202636</t>
+  </si>
+  <si>
+    <t>Richmond Street</t>
+  </si>
+  <si>
+    <t>RS202659</t>
+  </si>
+  <si>
+    <t>RS202737</t>
+  </si>
+  <si>
+    <t>RS205494</t>
+  </si>
+  <si>
+    <t>Carlisle Street</t>
+  </si>
+  <si>
+    <t>Harding Way West</t>
+  </si>
+  <si>
+    <t>RS205514</t>
+  </si>
+  <si>
+    <t>RS205761</t>
+  </si>
+  <si>
+    <t>RS206170</t>
+  </si>
+  <si>
+    <t>Gladstone Way</t>
+  </si>
+  <si>
+    <t>RS206230</t>
+  </si>
+  <si>
+    <t>Marshall Way</t>
+  </si>
+  <si>
+    <t>RS206486</t>
+  </si>
+  <si>
+    <t>RS212789</t>
+  </si>
+  <si>
+    <t>Dufferin Line</t>
   </si>
   <si>
     <t>Bennett Street</t>
   </si>
   <si>
-    <t>RS191298</t>
-  </si>
-  <si>
-    <t>Hickory Drive</t>
-  </si>
-  <si>
-    <t>Balsam Avenue South</t>
-  </si>
-  <si>
-    <t>Sherwood Way</t>
-  </si>
-  <si>
-    <t>RS191338</t>
-  </si>
-  <si>
-    <t>Tecumseh Way</t>
-  </si>
-  <si>
-    <t>RS191340</t>
-  </si>
-  <si>
-    <t>Dufferin Line</t>
-  </si>
-  <si>
-    <t>RS191399</t>
-  </si>
-  <si>
-    <t>Marshall Way</t>
-  </si>
-  <si>
-    <t>RS191439</t>
-  </si>
-  <si>
-    <t>Rossland Line</t>
-  </si>
-  <si>
-    <t>RS191601</t>
-  </si>
-  <si>
-    <t>Quarry Avenue West</t>
-  </si>
-  <si>
-    <t>RS189702</t>
-  </si>
-  <si>
-    <t>Laurel Avenue</t>
-  </si>
-  <si>
-    <t>Maitland Line</t>
-  </si>
-  <si>
-    <t>Prospect Avenue</t>
-  </si>
-  <si>
-    <t>RS189716</t>
-  </si>
-  <si>
-    <t>Robson Road</t>
-  </si>
-  <si>
-    <t>RS189766</t>
-  </si>
-  <si>
-    <t>Allan Way</t>
-  </si>
-  <si>
-    <t>RS189856</t>
-  </si>
-  <si>
-    <t>Edgewater Crescent</t>
-  </si>
-  <si>
-    <t>RS189934</t>
-  </si>
-  <si>
-    <t>Cambrian Boulevard</t>
-  </si>
-  <si>
-    <t>RS190046</t>
-  </si>
-  <si>
-    <t>Morris Crescent</t>
-  </si>
-  <si>
-    <t>RS190520</t>
-  </si>
-  <si>
-    <t>Lennox Line</t>
-  </si>
-  <si>
-    <t>Walker Avenue</t>
-  </si>
-  <si>
-    <t>Park Lawn Street</t>
-  </si>
-  <si>
-    <t>RS190562</t>
-  </si>
-  <si>
-    <t>RS190620</t>
-  </si>
-  <si>
-    <t>Richmond Street West</t>
-  </si>
-  <si>
-    <t>RS190657</t>
-  </si>
-  <si>
-    <t>RS190726</t>
-  </si>
-  <si>
-    <t>Warwick Crescent</t>
-  </si>
-  <si>
-    <t>RS190745</t>
-  </si>
-  <si>
-    <t>Pleasant Avenue</t>
-  </si>
-  <si>
-    <t>RS193375</t>
-  </si>
-  <si>
-    <t>Monarch Street</t>
-  </si>
-  <si>
-    <t>Winston Way</t>
-  </si>
-  <si>
-    <t>Canterbury Street</t>
-  </si>
-  <si>
-    <t>RS193419</t>
-  </si>
-  <si>
-    <t>Keegan Street</t>
-  </si>
-  <si>
-    <t>RS193509</t>
-  </si>
-  <si>
-    <t>RS193583</t>
-  </si>
-  <si>
-    <t>Chester Drive</t>
-  </si>
-  <si>
-    <t>RS193665</t>
-  </si>
-  <si>
-    <t>Vaughan Crescent</t>
-  </si>
-  <si>
-    <t>RS193767</t>
-  </si>
-  <si>
-    <t>Ashby Boulevard</t>
-  </si>
-  <si>
-    <t>RS190133</t>
-  </si>
-  <si>
-    <t>Norwood Way</t>
-  </si>
-  <si>
-    <t>Wilson Street</t>
-  </si>
-  <si>
-    <t>Maplewood Avenue</t>
-  </si>
-  <si>
-    <t>RS190176</t>
+    <t>RS212830</t>
+  </si>
+  <si>
+    <t>Sunnyside Crescent West</t>
+  </si>
+  <si>
+    <t>RS213033</t>
   </si>
   <si>
     <t>Rosedale Avenue</t>
   </si>
   <si>
-    <t>RS190271</t>
-  </si>
-  <si>
-    <t>RS190363</t>
-  </si>
-  <si>
-    <t>RS190379</t>
-  </si>
-  <si>
-    <t>Hillcrest Avenue</t>
-  </si>
-  <si>
-    <t>RS190419</t>
-  </si>
-  <si>
-    <t>RS180914</t>
-  </si>
-  <si>
-    <t>Poplar Crescent</t>
-  </si>
-  <si>
-    <t>Wellesley Street</t>
-  </si>
-  <si>
-    <t>Russell Road</t>
-  </si>
-  <si>
-    <t>RS180929</t>
-  </si>
-  <si>
-    <t>Linden Avenue</t>
-  </si>
-  <si>
-    <t>RS180999</t>
+    <t>RS213170</t>
+  </si>
+  <si>
+    <t>Farrell Road</t>
+  </si>
+  <si>
+    <t>RS213353</t>
+  </si>
+  <si>
+    <t>RS213473</t>
+  </si>
+  <si>
+    <t>RS204022</t>
+  </si>
+  <si>
+    <t>Hemlock Line</t>
+  </si>
+  <si>
+    <t>Conant Drive</t>
+  </si>
+  <si>
+    <t>RS204151</t>
+  </si>
+  <si>
+    <t>RS204191</t>
+  </si>
+  <si>
+    <t>RS204202</t>
+  </si>
+  <si>
+    <t>Dawson Line</t>
+  </si>
+  <si>
+    <t>RS204259</t>
+  </si>
+  <si>
+    <t>RS204272</t>
+  </si>
+  <si>
+    <t>RS201054</t>
+  </si>
+  <si>
+    <t>Jarvis Avenue</t>
+  </si>
+  <si>
+    <t>RS201143</t>
+  </si>
+  <si>
+    <t>Brant Crescent</t>
+  </si>
+  <si>
+    <t>RS201194</t>
+  </si>
+  <si>
+    <t>Hartley Avenue</t>
+  </si>
+  <si>
+    <t>RS201252</t>
+  </si>
+  <si>
+    <t>Heritage Line</t>
+  </si>
+  <si>
+    <t>RS201254</t>
+  </si>
+  <si>
+    <t>RS201269</t>
+  </si>
+  <si>
+    <t>RS201378</t>
+  </si>
+  <si>
+    <t>Bolton Street West</t>
+  </si>
+  <si>
+    <t>RS206490</t>
+  </si>
+  <si>
+    <t>Milton Line</t>
+  </si>
+  <si>
+    <t>RS206527</t>
+  </si>
+  <si>
+    <t>RS206529</t>
+  </si>
+  <si>
+    <t>Finch Boulevard</t>
+  </si>
+  <si>
+    <t>RS206721</t>
+  </si>
+  <si>
+    <t>Ramsay Avenue</t>
+  </si>
+  <si>
+    <t>RS206774</t>
+  </si>
+  <si>
+    <t>Devon Road</t>
+  </si>
+  <si>
+    <t>RS206793</t>
+  </si>
+  <si>
+    <t>Thompson Avenue</t>
+  </si>
+  <si>
+    <t>RS198340</t>
+  </si>
+  <si>
+    <t>Moore Drive</t>
+  </si>
+  <si>
+    <t>RS198490</t>
+  </si>
+  <si>
+    <t>Fraser Way</t>
+  </si>
+  <si>
+    <t>RS198497</t>
+  </si>
+  <si>
+    <t>RS198546</t>
+  </si>
+  <si>
+    <t>RS198554</t>
   </si>
   <si>
     <t>Harcourt Road</t>
   </si>
   <si>
-    <t>RS181135</t>
-  </si>
-  <si>
-    <t>Trillium Drive</t>
-  </si>
-  <si>
-    <t>RS181262</t>
-  </si>
-  <si>
-    <t>Coleridge Avenue</t>
-  </si>
-  <si>
-    <t>RS181327</t>
-  </si>
-  <si>
-    <t>Leeds Avenue</t>
-  </si>
-  <si>
-    <t>RS181380</t>
-  </si>
-  <si>
-    <t>Rosedale Drive West</t>
-  </si>
-  <si>
-    <t>RS193127</t>
-  </si>
-  <si>
-    <t>Riverside Way</t>
-  </si>
-  <si>
-    <t>Quinlan Drive</t>
-  </si>
-  <si>
-    <t>Ramsay Avenue</t>
-  </si>
-  <si>
-    <t>RS193307</t>
-  </si>
-  <si>
-    <t>RS193324</t>
-  </si>
-  <si>
-    <t>Bancroft Road</t>
-  </si>
-  <si>
-    <t>RS193343</t>
-  </si>
-  <si>
-    <t>Dunbar Boulevard</t>
-  </si>
-  <si>
-    <t>RS193354</t>
-  </si>
-  <si>
-    <t>Elliot Boulevard</t>
-  </si>
-  <si>
-    <t>RS193372</t>
-  </si>
-  <si>
-    <t>Rutherford Boulevard</t>
-  </si>
-  <si>
-    <t>RS184380</t>
-  </si>
-  <si>
-    <t>Holland Crescent</t>
-  </si>
-  <si>
-    <t>LKS</t>
-  </si>
-  <si>
-    <t>RS184434</t>
-  </si>
-  <si>
-    <t>RS184548</t>
-  </si>
-  <si>
-    <t>Willow Avenue</t>
-  </si>
-  <si>
-    <t>RS184739</t>
-  </si>
-  <si>
-    <t>O'Connor Boulevard East</t>
-  </si>
-  <si>
-    <t>RS184768</t>
-  </si>
-  <si>
-    <t>RS184781</t>
-  </si>
-  <si>
-    <t>RS184819</t>
-  </si>
-  <si>
-    <t>Ardagh Road</t>
-  </si>
-  <si>
-    <t>RS190904</t>
-  </si>
-  <si>
-    <t>Barclay Avenue</t>
-  </si>
-  <si>
-    <t>Tiffany Drive</t>
-  </si>
-  <si>
-    <t>RS191021</t>
-  </si>
-  <si>
-    <t>RS191219</t>
-  </si>
-  <si>
-    <t>Haddon Way</t>
-  </si>
-  <si>
-    <t>RS191221</t>
-  </si>
-  <si>
-    <t>Cumberland Avenue</t>
-  </si>
-  <si>
-    <t>RS191229</t>
-  </si>
-  <si>
-    <t>Stafford Boulevard</t>
-  </si>
-  <si>
-    <t>RS191232</t>
-  </si>
-  <si>
-    <t>Inglewood Drive South</t>
-  </si>
-  <si>
-    <t>RS193801</t>
-  </si>
-  <si>
-    <t>Bramble Boulevard</t>
+    <t>RS198721</t>
+  </si>
+  <si>
+    <t>RS198855</t>
+  </si>
+  <si>
+    <t>RS207838</t>
+  </si>
+  <si>
+    <t>Cedar Street</t>
+  </si>
+  <si>
+    <t>RS207848</t>
+  </si>
+  <si>
+    <t>RS207900</t>
+  </si>
+  <si>
+    <t>Newbury Street</t>
+  </si>
+  <si>
+    <t>RS207947</t>
+  </si>
+  <si>
+    <t>RS207954</t>
+  </si>
+  <si>
+    <t>RS208008</t>
   </si>
   <si>
     <t>Clifton Way</t>
   </si>
   <si>
-    <t>Locke Street East</t>
-  </si>
-  <si>
-    <t>RS193927</t>
-  </si>
-  <si>
-    <t>Merritt Avenue</t>
-  </si>
-  <si>
-    <t>RS194062</t>
-  </si>
-  <si>
-    <t>Parkside Crescent</t>
-  </si>
-  <si>
-    <t>RS194132</t>
-  </si>
-  <si>
-    <t>RS194135</t>
-  </si>
-  <si>
-    <t>Wildwood Way</t>
-  </si>
-  <si>
-    <t>RS194329</t>
-  </si>
-  <si>
-    <t>RS196007</t>
-  </si>
-  <si>
-    <t>Briar Street</t>
-  </si>
-  <si>
-    <t>Sheridan Drive</t>
-  </si>
-  <si>
-    <t>RS196091</t>
-  </si>
-  <si>
-    <t>RS196281</t>
-  </si>
-  <si>
-    <t>Abbott Boulevard</t>
-  </si>
-  <si>
-    <t>RS196345</t>
-  </si>
-  <si>
-    <t>Gladstone Way</t>
-  </si>
-  <si>
-    <t>RS196433</t>
-  </si>
-  <si>
-    <t>Grove Boulevard</t>
-  </si>
-  <si>
-    <t>RS196476</t>
-  </si>
-  <si>
-    <t>Kent Way</t>
-  </si>
-  <si>
-    <t>RS182868</t>
-  </si>
-  <si>
-    <t>Edison Street</t>
-  </si>
-  <si>
-    <t>Farrell Road</t>
-  </si>
-  <si>
-    <t>RS182903</t>
-  </si>
-  <si>
-    <t>RS182962</t>
-  </si>
-  <si>
-    <t>Howard Avenue</t>
-  </si>
-  <si>
-    <t>RS182974</t>
-  </si>
-  <si>
-    <t>RS183037</t>
-  </si>
-  <si>
-    <t>RS183072</t>
-  </si>
-  <si>
-    <t>RS183185</t>
-  </si>
-  <si>
-    <t>Chapel Avenue</t>
-  </si>
-  <si>
-    <t>RS185676</t>
-  </si>
-  <si>
-    <t>RS185743</t>
-  </si>
-  <si>
-    <t>Canterbury Street North</t>
-  </si>
-  <si>
-    <t>RS185787</t>
-  </si>
-  <si>
-    <t>Lancaster Street</t>
-  </si>
-  <si>
-    <t>RS185902</t>
-  </si>
-  <si>
-    <t>Knox Line</t>
-  </si>
-  <si>
-    <t>RS185924</t>
-  </si>
-  <si>
-    <t>Durham Street</t>
-  </si>
-  <si>
-    <t>RS185933</t>
-  </si>
-  <si>
-    <t>Scarlett Road</t>
-  </si>
-  <si>
-    <t>RS185955</t>
-  </si>
-  <si>
-    <t>RS183202</t>
-  </si>
-  <si>
-    <t>Tobin Street</t>
-  </si>
-  <si>
-    <t>RS183241</t>
-  </si>
-  <si>
-    <t>RS183381</t>
-  </si>
-  <si>
-    <t>Whitney Drive</t>
-  </si>
-  <si>
-    <t>RS183474</t>
-  </si>
-  <si>
-    <t>Finch Boulevard</t>
-  </si>
-  <si>
-    <t>RS183701</t>
-  </si>
-  <si>
-    <t>Valleyview Drive</t>
-  </si>
-  <si>
-    <t>RS184289</t>
-  </si>
-  <si>
-    <t>RS184305</t>
-  </si>
-  <si>
-    <t>Jameson Boulevard</t>
-  </si>
-  <si>
-    <t>RS191938</t>
-  </si>
-  <si>
-    <t>Cotswold Boulevard</t>
-  </si>
-  <si>
-    <t>Juniper Road</t>
-  </si>
-  <si>
-    <t>RS191961</t>
-  </si>
-  <si>
-    <t>Kipling Road</t>
-  </si>
-  <si>
-    <t>RS192009</t>
-  </si>
-  <si>
-    <t>Trafalgar Boulevard</t>
-  </si>
-  <si>
-    <t>RS192078</t>
-  </si>
-  <si>
-    <t>Palmer Line</t>
-  </si>
-  <si>
-    <t>RS192156</t>
-  </si>
-  <si>
-    <t>RS192368</t>
-  </si>
-  <si>
-    <t>RS195670</t>
-  </si>
-  <si>
-    <t>Cobden Avenue</t>
-  </si>
-  <si>
-    <t>Essex Avenue</t>
-  </si>
-  <si>
-    <t>MPF</t>
-  </si>
-  <si>
-    <t>RS195760</t>
-  </si>
-  <si>
-    <t>Sydenham Street</t>
-  </si>
-  <si>
-    <t>RS195786</t>
-  </si>
-  <si>
-    <t>RS195797</t>
-  </si>
-  <si>
-    <t>RS195868</t>
-  </si>
-  <si>
-    <t>Lambton Line West</t>
-  </si>
-  <si>
-    <t>RS195991</t>
-  </si>
-  <si>
-    <t>Dalhousie Street</t>
-  </si>
-  <si>
-    <t>RS192616</t>
-  </si>
-  <si>
-    <t>Glenview Drive</t>
-  </si>
-  <si>
-    <t>Doherty Street West</t>
-  </si>
-  <si>
-    <t>Conant Drive</t>
-  </si>
-  <si>
-    <t>RS192667</t>
-  </si>
-  <si>
-    <t>RS192719</t>
-  </si>
-  <si>
-    <t>RS192740</t>
-  </si>
-  <si>
-    <t>Mackenzie Street West</t>
-  </si>
-  <si>
-    <t>RS193012</t>
-  </si>
-  <si>
-    <t>RS193103</t>
-  </si>
-  <si>
-    <t>RS185232</t>
-  </si>
-  <si>
-    <t>Raglan Crescent</t>
-  </si>
-  <si>
-    <t>RS185368</t>
-  </si>
-  <si>
-    <t>Macdonald Road</t>
-  </si>
-  <si>
-    <t>RS185460</t>
-  </si>
-  <si>
-    <t>RS185538</t>
-  </si>
-  <si>
-    <t>Keats Avenue North</t>
-  </si>
-  <si>
-    <t>RS185570</t>
-  </si>
-  <si>
-    <t>RS185591</t>
-  </si>
-  <si>
-    <t>Oakdale Line</t>
-  </si>
-  <si>
-    <t>RS185672</t>
-  </si>
-  <si>
-    <t>Tiffany Street West</t>
-  </si>
-  <si>
-    <t>RS181547</t>
-  </si>
-  <si>
-    <t>RS181561</t>
-  </si>
-  <si>
-    <t>Heritage Way South</t>
-  </si>
-  <si>
-    <t>RS181572</t>
-  </si>
-  <si>
-    <t>RS181735</t>
-  </si>
-  <si>
-    <t>RS181892</t>
-  </si>
-  <si>
-    <t>Burnside Line</t>
-  </si>
-  <si>
-    <t>RS181973</t>
-  </si>
-  <si>
-    <t>Waterloo Road</t>
-  </si>
-  <si>
-    <t>RS182028</t>
-  </si>
-  <si>
-    <t>RS191631</t>
-  </si>
-  <si>
-    <t>Cornwall Avenue</t>
-  </si>
-  <si>
-    <t>Ferndale Street</t>
-  </si>
-  <si>
-    <t>RS191639</t>
-  </si>
-  <si>
-    <t>RS191692</t>
-  </si>
-  <si>
-    <t>McCormick Avenue</t>
-  </si>
-  <si>
-    <t>RS191778</t>
-  </si>
-  <si>
-    <t>Lambton Crescent</t>
-  </si>
-  <si>
-    <t>RS191804</t>
-  </si>
-  <si>
-    <t>RS191847</t>
-  </si>
-  <si>
-    <t>RS195378</t>
-  </si>
-  <si>
-    <t>RDG</t>
-  </si>
-  <si>
-    <t>RS195398</t>
-  </si>
-  <si>
-    <t>RS195430</t>
-  </si>
-  <si>
-    <t>RS195453</t>
-  </si>
-  <si>
-    <t>RS195558</t>
-  </si>
-  <si>
-    <t>Bruce Street</t>
-  </si>
-  <si>
-    <t>RS195577</t>
-  </si>
-  <si>
-    <t>Radcliffe Road</t>
-  </si>
-  <si>
-    <t>RS187346</t>
-  </si>
-  <si>
-    <t>Dalhousie Street East</t>
-  </si>
-  <si>
-    <t>RS187668</t>
-  </si>
-  <si>
-    <t>RS187869</t>
-  </si>
-  <si>
-    <t>Lawrence Way West</t>
-  </si>
-  <si>
-    <t>RS187873</t>
-  </si>
-  <si>
-    <t>RS187874</t>
-  </si>
-  <si>
-    <t>Carlton Street</t>
-  </si>
-  <si>
-    <t>RS187994</t>
-  </si>
-  <si>
-    <t>Arden Street</t>
-  </si>
-  <si>
-    <t>RS194936</t>
-  </si>
-  <si>
-    <t>Gardner Boulevard</t>
-  </si>
-  <si>
-    <t>Aspen Avenue</t>
-  </si>
-  <si>
-    <t>RS195104</t>
-  </si>
-  <si>
-    <t>Wilson Avenue North</t>
-  </si>
-  <si>
-    <t>RS195131</t>
-  </si>
-  <si>
-    <t>Buckingham Road</t>
-  </si>
-  <si>
-    <t>RS195177</t>
-  </si>
-  <si>
-    <t>RS195227</t>
-  </si>
-  <si>
-    <t>RS195297</t>
-  </si>
-  <si>
-    <t>Brock Way</t>
-  </si>
-  <si>
-    <t>RS196561</t>
-  </si>
-  <si>
-    <t>Eastwood Line</t>
-  </si>
-  <si>
-    <t>RS196639</t>
-  </si>
-  <si>
-    <t>RS196701</t>
-  </si>
-  <si>
-    <t>Thompson Avenue</t>
-  </si>
-  <si>
-    <t>RS196943</t>
-  </si>
-  <si>
-    <t>RS197031</t>
-  </si>
-  <si>
-    <t>RS197115</t>
-  </si>
-  <si>
-    <t>Upton Road</t>
-  </si>
-  <si>
-    <t>RS186045</t>
-  </si>
-  <si>
-    <t>Gibson Boulevard</t>
-  </si>
-  <si>
-    <t>RS186235</t>
-  </si>
-  <si>
-    <t>RS186581</t>
-  </si>
-  <si>
-    <t>RS186770</t>
-  </si>
-  <si>
-    <t>RS186801</t>
-  </si>
-  <si>
-    <t>RS186809</t>
-  </si>
-  <si>
-    <t>Halton Line</t>
-  </si>
-  <si>
-    <t>RS186819</t>
-  </si>
-  <si>
-    <t>RS188849</t>
-  </si>
-  <si>
-    <t>Lockhart Drive</t>
-  </si>
-  <si>
-    <t>Irving Avenue</t>
-  </si>
-  <si>
-    <t>RS188860</t>
-  </si>
-  <si>
-    <t>RS188906</t>
-  </si>
-  <si>
-    <t>RS188958</t>
-  </si>
-  <si>
-    <t>Dawson Line</t>
-  </si>
-  <si>
-    <t>RS188978</t>
-  </si>
-  <si>
-    <t>Madison Road</t>
-  </si>
-  <si>
-    <t>RS189035</t>
-  </si>
-  <si>
-    <t>Walnut Avenue</t>
-  </si>
-  <si>
-    <t>RS184827</t>
-  </si>
-  <si>
-    <t>Rockwood Line</t>
-  </si>
-  <si>
-    <t>O'Connor Crescent</t>
-  </si>
-  <si>
-    <t>RS184835</t>
-  </si>
-  <si>
-    <t>RS184882</t>
-  </si>
-  <si>
-    <t>Victoria Park Drive East</t>
-  </si>
-  <si>
-    <t>RS184955</t>
-  </si>
-  <si>
-    <t>Manor Way</t>
-  </si>
-  <si>
-    <t>RS184984</t>
-  </si>
-  <si>
-    <t>RS185026</t>
-  </si>
-  <si>
-    <t>RS185073</t>
-  </si>
-  <si>
-    <t>Lawrence Road</t>
-  </si>
-  <si>
-    <t>RS182315</t>
-  </si>
-  <si>
-    <t>Regent Line West</t>
-  </si>
-  <si>
-    <t>RS182402</t>
-  </si>
-  <si>
-    <t>Heritage Line</t>
-  </si>
-  <si>
-    <t>RS182407</t>
-  </si>
-  <si>
-    <t>RS182433</t>
-  </si>
-  <si>
-    <t>Delaware Way</t>
-  </si>
-  <si>
-    <t>RS182466</t>
-  </si>
-  <si>
-    <t>RS182494</t>
-  </si>
-  <si>
-    <t>RS182659</t>
-  </si>
-  <si>
-    <t>RS192440</t>
-  </si>
-  <si>
-    <t>Southgate Street</t>
-  </si>
-  <si>
-    <t>RS192484</t>
-  </si>
-  <si>
-    <t>Greenwood Street</t>
-  </si>
-  <si>
-    <t>RS192505</t>
-  </si>
-  <si>
-    <t>RS192573</t>
-  </si>
-  <si>
-    <t>RS192591</t>
-  </si>
-  <si>
-    <t>RS192595</t>
-  </si>
-  <si>
-    <t>RS194416</t>
-  </si>
-  <si>
-    <t>Charlton Drive</t>
-  </si>
-  <si>
-    <t>Mohawk Street</t>
-  </si>
-  <si>
-    <t>RS194437</t>
-  </si>
-  <si>
-    <t>Emerson Drive</t>
-  </si>
-  <si>
-    <t>RS194684</t>
-  </si>
-  <si>
-    <t>Simcoe Boulevard</t>
-  </si>
-  <si>
-    <t>RS194738</t>
-  </si>
-  <si>
-    <t>RS194748</t>
-  </si>
-  <si>
-    <t>RS194929</t>
-  </si>
-  <si>
-    <t>Spencer Boulevard</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -1331,7 +1367,7 @@
     <t>2025-26 (t)</t>
   </si>
   <si>
-    <t>Rock salt spread on each yard's Priority 1 arterial circuits, 1 November to 31 March, contract circuits included.</t>
+    <t>Rock salt spread on each yard's Priority 1 arterial circuits, 1 November to 31 March, each circuit under the yard it belonged to that winter, contract circuits included.</t>
   </si>
   <si>
     <t>Data pulled 25 September 2026: legacy AVL segment-by-shift summaries (November 2021 to March 2023, kilograms, local time) and telematics segment passes (from 1 October 2023, tonnes, UTC, taken to Eastern time).</t>
@@ -1340,7 +1376,7 @@
     <t>Legacy segment ids taken to the current segments through the 2023 GIS crosswalk by length share.</t>
   </si>
   <si>
-    <t>Winters run 1 November to 31 March. Each winter's salt is divided by its Winter Severity Index from the storm log (2021-22 63.4, 2022-23 50.1, 2023-24 38.9, 2024-25 67.2, 2025-26 52.6 points).</t>
+    <t>Winters run 1 November to 31 March. Each winter's salt is divided by its Winter Severity Index from the storm log (2021-22 63.4, 2022-23 50.1, 2023-24 38.9, 2024-25 67.2, 2025-26 58.4 points).</t>
   </si>
   <si>
     <t>Planning severity 61.7 WSI points (winter maintenance plan 2026-27, section 4). Seasonal tonnage per RO-PR-07 4.2, rounded to the nearest 100 t.</t>
@@ -1415,7 +1451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1438,6 +1474,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1797,7 +1834,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1826,7 +1863,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1834,7 +1871,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="8">
-        <v>-0.655</v>
+        <v>-0.663</v>
       </c>
     </row>
   </sheetData>
@@ -1900,13 +1937,13 @@
         <v>25</v>
       </c>
       <c r="F2" s="7">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="G2" s="7">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="H2" s="10">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1926,13 +1963,13 @@
         <v>25</v>
       </c>
       <c r="F3" s="7">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="G3" s="7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H3" s="10">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1952,13 +1989,13 @@
         <v>25</v>
       </c>
       <c r="F4" s="7">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="G4" s="7">
-        <v>0.18</v>
+        <v>2.76</v>
       </c>
       <c r="H4" s="10">
-        <v>9.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1978,13 +2015,13 @@
         <v>25</v>
       </c>
       <c r="F5" s="7">
-        <v>2.26</v>
+        <v>1.54</v>
       </c>
       <c r="G5" s="7">
-        <v>0.5600000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="H5" s="10">
-        <v>13.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2004,13 +2041,13 @@
         <v>25</v>
       </c>
       <c r="F6" s="7">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="G6" s="7">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="H6" s="10">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2030,13 +2067,13 @@
         <v>25</v>
       </c>
       <c r="F7" s="7">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="G7" s="7">
-        <v>0.75</v>
+        <v>1.7</v>
       </c>
       <c r="H7" s="10">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2056,13 +2093,13 @@
         <v>25</v>
       </c>
       <c r="F8" s="7">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="G8" s="7">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="H8" s="10">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2082,13 +2119,13 @@
         <v>25</v>
       </c>
       <c r="F9" s="7">
-        <v>1.28</v>
+        <v>2.48</v>
       </c>
       <c r="G9" s="7">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="H9" s="10">
-        <v>5.8</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2108,13 +2145,13 @@
         <v>25</v>
       </c>
       <c r="F10" s="7">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="G10" s="7">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="10">
-        <v>9.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2134,13 +2171,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="7">
-        <v>1.96</v>
+        <v>3.56</v>
       </c>
       <c r="G11" s="7">
-        <v>2.69</v>
+        <v>1.5</v>
       </c>
       <c r="H11" s="10">
-        <v>8.800000000000001</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2160,13 +2197,13 @@
         <v>25</v>
       </c>
       <c r="F12" s="7">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="G12" s="7">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="H12" s="10">
-        <v>6.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2186,13 +2223,13 @@
         <v>25</v>
       </c>
       <c r="F13" s="7">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="G13" s="7">
-        <v>1.99</v>
+        <v>2.44</v>
       </c>
       <c r="H13" s="10">
-        <v>6.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2200,363 +2237,363 @@
         <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="7">
-        <v>2.5</v>
+        <v>4.88</v>
       </c>
       <c r="G14" s="7">
-        <v>0.39</v>
+        <v>1.45</v>
       </c>
       <c r="H14" s="10">
-        <v>15</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="7">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="G15" s="7">
-        <v>0.28</v>
+        <v>1.35</v>
       </c>
       <c r="H15" s="10">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
         <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="7">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="G16" s="7">
-        <v>1</v>
+        <v>3.84</v>
       </c>
       <c r="H16" s="10">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="7">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="G17" s="7">
-        <v>1.13</v>
+        <v>1.96</v>
       </c>
       <c r="H17" s="10">
-        <v>13.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="7">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="G18" s="7">
-        <v>2.83</v>
+        <v>1.22</v>
       </c>
       <c r="H18" s="10">
-        <v>11.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
         <v>62</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="7">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="G19" s="7">
-        <v>0.48</v>
+        <v>1.05</v>
       </c>
       <c r="H19" s="10">
-        <v>15.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
         <v>64</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="7">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="G20" s="7">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="H20" s="10">
-        <v>8.699999999999999</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
         <v>66</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>67</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>69</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="7">
-        <v>1.68</v>
+        <v>0.9</v>
       </c>
       <c r="G21" s="7">
-        <v>1.69</v>
+        <v>2.59</v>
       </c>
       <c r="H21" s="10">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>70</v>
-      </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="7">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="G22" s="7">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="H22" s="10">
-        <v>11.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="7">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="G23" s="7">
-        <v>0.61</v>
+        <v>1.61</v>
       </c>
       <c r="H23" s="10">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="7">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="G24" s="7">
-        <v>3.59</v>
+        <v>1.68</v>
       </c>
       <c r="H24" s="10">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>77</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="7">
-        <v>2.12</v>
+        <v>0.9</v>
       </c>
       <c r="G25" s="7">
-        <v>0.4</v>
+        <v>3.22</v>
       </c>
       <c r="H25" s="10">
-        <v>12.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
         <v>78</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" t="s">
-        <v>79</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="7">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="G26" s="7">
-        <v>0.85</v>
+        <v>1.64</v>
       </c>
       <c r="H26" s="10">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
         <v>80</v>
       </c>
-      <c r="B27" t="s">
-        <v>67</v>
-      </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="7">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="G27" s="7">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="H27" s="10">
-        <v>6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2564,961 +2601,961 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
         <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="7">
-        <v>1.84</v>
+        <v>1.48</v>
       </c>
       <c r="G28" s="7">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="H28" s="10">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s">
         <v>83</v>
       </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="7">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="G29" s="7">
-        <v>0.51</v>
+        <v>1.55</v>
       </c>
       <c r="H29" s="10">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="7">
-        <v>2.58</v>
+        <v>1.68</v>
       </c>
       <c r="G30" s="7">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="H30" s="10">
-        <v>14.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
       </c>
       <c r="F31" s="7">
-        <v>2.26</v>
+        <v>1.22</v>
       </c>
       <c r="G31" s="7">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="H31" s="10">
-        <v>12</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" s="7">
-        <v>1.92</v>
+        <v>1.22</v>
       </c>
       <c r="G32" s="7">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="H32" s="10">
-        <v>10.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
         <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="7">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="G33" s="7">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="H33" s="10">
-        <v>11.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
         <v>96</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>99</v>
       </c>
       <c r="E34" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="7">
-        <v>3.52</v>
+        <v>1.7</v>
       </c>
       <c r="G34" s="7">
-        <v>2.29</v>
+        <v>1.38</v>
       </c>
       <c r="H34" s="10">
-        <v>16.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G35" s="7">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="H35" s="10">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="7">
-        <v>3.16</v>
+        <v>2.34</v>
       </c>
       <c r="G36" s="7">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="H36" s="10">
-        <v>15.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="7">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="G37" s="7">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="H37" s="10">
-        <v>10.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="7">
-        <v>4.52</v>
+        <v>1.6</v>
       </c>
       <c r="G38" s="7">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="H38" s="10">
-        <v>27.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="7">
-        <v>5.08</v>
+        <v>1.9</v>
       </c>
       <c r="G39" s="7">
-        <v>0.61</v>
+        <v>1.58</v>
       </c>
       <c r="H39" s="10">
-        <v>29.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="7">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="G40" s="7">
-        <v>0.72</v>
+        <v>2.86</v>
       </c>
       <c r="H40" s="10">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="7">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="G41" s="7">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="H41" s="10">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="7">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="G42" s="7">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="H42" s="10">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="E43" t="s">
         <v>25</v>
       </c>
       <c r="F43" s="7">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="G43" s="7">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H43" s="10">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="7">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="G44" s="7">
-        <v>0.91</v>
+        <v>1.38</v>
       </c>
       <c r="H44" s="10">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C45" t="s">
         <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
       </c>
       <c r="F45" s="7">
-        <v>1.64</v>
+        <v>2.28</v>
       </c>
       <c r="G45" s="7">
-        <v>2.35</v>
+        <v>1.34</v>
       </c>
       <c r="H45" s="10">
-        <v>7.7</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" t="s">
         <v>122</v>
-      </c>
-      <c r="B46" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="7">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="G46" s="7">
-        <v>3.37</v>
+        <v>1.1</v>
       </c>
       <c r="H46" s="10">
-        <v>8.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="7">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="G47" s="7">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="H47" s="10">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
       </c>
       <c r="F48" s="7">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="G48" s="7">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="H48" s="10">
-        <v>9.5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
       </c>
       <c r="F49" s="7">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="G49" s="7">
-        <v>1.04</v>
+        <v>2.09</v>
       </c>
       <c r="H49" s="10">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" t="s">
         <v>130</v>
-      </c>
-      <c r="D50" t="s">
-        <v>132</v>
       </c>
       <c r="E50" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="7">
-        <v>2.48</v>
+        <v>0.92</v>
       </c>
       <c r="G50" s="7">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="H50" s="10">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
         <v>25</v>
       </c>
       <c r="F51" s="7">
-        <v>2.46</v>
+        <v>0.86</v>
       </c>
       <c r="G51" s="7">
-        <v>0.6899999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="H51" s="10">
-        <v>14.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="7">
-        <v>1.74</v>
+        <v>1.02</v>
       </c>
       <c r="G52" s="7">
-        <v>3.59</v>
+        <v>2.66</v>
       </c>
       <c r="H52" s="10">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" t="s">
         <v>136</v>
-      </c>
-      <c r="C53" t="s">
-        <v>138</v>
-      </c>
-      <c r="D53" t="s">
-        <v>140</v>
       </c>
       <c r="E53" t="s">
         <v>25</v>
       </c>
       <c r="F53" s="7">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="G53" s="7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H53" s="10">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B54" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" t="s">
         <v>136</v>
       </c>
-      <c r="C54" t="s">
-        <v>140</v>
-      </c>
       <c r="D54" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
       </c>
       <c r="F54" s="7">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G54" s="7">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="H54" s="10">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E55" t="s">
         <v>25</v>
       </c>
       <c r="F55" s="7">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="G55" s="7">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="H55" s="10">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
       </c>
       <c r="F56" s="7">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="G56" s="7">
-        <v>2.67</v>
+        <v>1.86</v>
       </c>
       <c r="H56" s="10">
-        <v>5.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C57" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" t="s">
         <v>144</v>
-      </c>
-      <c r="D57" t="s">
-        <v>22</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" s="7">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G57" s="7">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="H57" s="10">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
         <v>146</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" t="s">
         <v>147</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
         <v>148</v>
       </c>
-      <c r="D58" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
       <c r="F58" s="7">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
       <c r="G58" s="7">
-        <v>3.34</v>
+        <v>1.54</v>
       </c>
       <c r="H58" s="10">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" t="s">
         <v>147</v>
       </c>
-      <c r="C59" t="s">
-        <v>149</v>
-      </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F59" s="7">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="G59" s="7">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="H59" s="10">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" t="s">
         <v>151</v>
       </c>
-      <c r="D60" t="s">
-        <v>153</v>
-      </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F60" s="7">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="G60" s="7">
-        <v>3.38</v>
+        <v>1.39</v>
       </c>
       <c r="H60" s="10">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" t="s">
         <v>153</v>
       </c>
-      <c r="D61" t="s">
-        <v>155</v>
-      </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F61" s="7">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="G61" s="7">
-        <v>0.59</v>
+        <v>1.92</v>
       </c>
       <c r="H61" s="10">
-        <v>10.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C62" t="s">
+        <v>153</v>
+      </c>
+      <c r="D62" t="s">
         <v>155</v>
       </c>
-      <c r="D62" t="s">
-        <v>157</v>
-      </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F62" s="7">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="G62" s="7">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="H62" s="10">
-        <v>7.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
         <v>157</v>
       </c>
-      <c r="D63" t="s">
-        <v>159</v>
-      </c>
       <c r="E63" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F63" s="7">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="G63" s="7">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="H63" s="10">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" t="s">
         <v>160</v>
-      </c>
-      <c r="B64" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" t="s">
-        <v>159</v>
       </c>
       <c r="D64" t="s">
         <v>161</v>
       </c>
       <c r="E64" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F64" s="7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G64" s="7">
-        <v>0.78</v>
+        <v>1.84</v>
       </c>
       <c r="H64" s="10">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -3526,337 +3563,337 @@
         <v>162</v>
       </c>
       <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>161</v>
+      </c>
+      <c r="D65" t="s">
         <v>163</v>
       </c>
-      <c r="C65" t="s">
-        <v>164</v>
-      </c>
-      <c r="D65" t="s">
-        <v>165</v>
-      </c>
       <c r="E65" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F65" s="7">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="G65" s="7">
-        <v>2.37</v>
+        <v>0.86</v>
       </c>
       <c r="H65" s="10">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B66" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" t="s">
         <v>163</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>165</v>
       </c>
-      <c r="D66" t="s">
-        <v>149</v>
-      </c>
       <c r="E66" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F66" s="7">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="G66" s="7">
-        <v>0.8</v>
+        <v>2.09</v>
       </c>
       <c r="H66" s="10">
-        <v>8.199999999999999</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" t="s">
         <v>167</v>
       </c>
-      <c r="B67" t="s">
-        <v>163</v>
-      </c>
-      <c r="C67" t="s">
-        <v>149</v>
-      </c>
-      <c r="D67" t="s">
-        <v>168</v>
-      </c>
       <c r="E67" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F67" s="7">
-        <v>0.9399999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="G67" s="7">
-        <v>0.99</v>
+        <v>1.36</v>
       </c>
       <c r="H67" s="10">
-        <v>5.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F68" s="7">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="G68" s="7">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="H68" s="10">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F69" s="7">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="G69" s="7">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="H69" s="10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F70" s="7">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="G70" s="7">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="H70" s="10">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F71" s="7">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="G71" s="7">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="H71" s="10">
-        <v>7.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D72" t="s">
         <v>176</v>
       </c>
-      <c r="D72" t="s">
-        <v>165</v>
-      </c>
       <c r="E72" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F72" s="7">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="G72" s="7">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="H72" s="10">
-        <v>12.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E73" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F73" s="7">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="G73" s="7">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="H73" s="10">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C74" t="s">
+        <v>178</v>
+      </c>
+      <c r="D74" t="s">
         <v>180</v>
       </c>
-      <c r="D74" t="s">
-        <v>182</v>
-      </c>
       <c r="E74" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F74" s="7">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="G74" s="7">
-        <v>0.36</v>
+        <v>2.59</v>
       </c>
       <c r="H74" s="10">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C75" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" t="s">
         <v>182</v>
       </c>
-      <c r="D75" t="s">
-        <v>164</v>
-      </c>
       <c r="E75" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F75" s="7">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="G75" s="7">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H75" s="10">
-        <v>8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F76" s="7">
-        <v>2.02</v>
+        <v>1.2</v>
       </c>
       <c r="G76" s="7">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="H76" s="10">
-        <v>10.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>184</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
         <v>185</v>
-      </c>
-      <c r="B77" t="s">
-        <v>52</v>
-      </c>
-      <c r="C77" t="s">
-        <v>59</v>
       </c>
       <c r="D77" t="s">
         <v>186</v>
       </c>
       <c r="E77" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F77" s="7">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G77" s="7">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="H77" s="10">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -3864,337 +3901,337 @@
         <v>187</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D78" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="E78" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F78" s="7">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="G78" s="7">
-        <v>0.29</v>
+        <v>1.84</v>
       </c>
       <c r="H78" s="10">
-        <v>8.699999999999999</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B79" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E79" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F79" s="7">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="G79" s="7">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="H79" s="10">
-        <v>9.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>190</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" t="s">
         <v>191</v>
       </c>
-      <c r="B80" t="s">
-        <v>188</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" t="s">
-        <v>192</v>
-      </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F80" s="7">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="G80" s="7">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H80" s="10">
-        <v>6.9</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" t="s">
         <v>193</v>
       </c>
-      <c r="B81" t="s">
-        <v>188</v>
-      </c>
-      <c r="C81" t="s">
-        <v>192</v>
-      </c>
-      <c r="D81" t="s">
-        <v>194</v>
-      </c>
       <c r="E81" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F81" s="7">
-        <v>0.96</v>
+        <v>1.24</v>
       </c>
       <c r="G81" s="7">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="H81" s="10">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>194</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>193</v>
+      </c>
+      <c r="D82" t="s">
         <v>195</v>
       </c>
-      <c r="B82" t="s">
-        <v>188</v>
-      </c>
-      <c r="C82" t="s">
-        <v>194</v>
-      </c>
-      <c r="D82" t="s">
-        <v>196</v>
-      </c>
       <c r="E82" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F82" s="7">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="G82" s="7">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="H82" s="10">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D83" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E83" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F83" s="7">
-        <v>2.28</v>
+        <v>1</v>
       </c>
       <c r="G83" s="7">
-        <v>0.5600000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="H83" s="10">
-        <v>13.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>197</v>
+      </c>
+      <c r="B84" t="s">
+        <v>110</v>
+      </c>
+      <c r="C84" t="s">
+        <v>198</v>
+      </c>
+      <c r="D84" t="s">
         <v>199</v>
       </c>
-      <c r="B84" t="s">
-        <v>200</v>
-      </c>
-      <c r="C84" t="s">
-        <v>201</v>
-      </c>
-      <c r="D84" t="s">
-        <v>202</v>
-      </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F84" s="7">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="G84" s="7">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="H84" s="10">
-        <v>12.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C85" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D85" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E85" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F85" s="7">
-        <v>4.28</v>
+        <v>1.82</v>
       </c>
       <c r="G85" s="7">
-        <v>0.66</v>
+        <v>1.25</v>
       </c>
       <c r="H85" s="10">
-        <v>24.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E86" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F86" s="7">
-        <v>2.32</v>
+        <v>1.3</v>
       </c>
       <c r="G86" s="7">
-        <v>0.88</v>
+        <v>1.67</v>
       </c>
       <c r="H86" s="10">
-        <v>13.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B87" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D87" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="E87" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F87" s="7">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="G87" s="7">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="H87" s="10">
-        <v>11</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F88" s="7">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="G88" s="7">
-        <v>2.71</v>
+        <v>1.01</v>
       </c>
       <c r="H88" s="10">
-        <v>8.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C89" t="s">
+        <v>207</v>
+      </c>
+      <c r="D89" t="s">
         <v>209</v>
       </c>
-      <c r="D89" t="s">
-        <v>123</v>
-      </c>
       <c r="E89" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F89" s="7">
-        <v>3.84</v>
+        <v>1.42</v>
       </c>
       <c r="G89" s="7">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="H89" s="10">
-        <v>17.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
         <v>211</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>212</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>213</v>
       </c>
-      <c r="D90" t="s">
-        <v>53</v>
-      </c>
       <c r="E90" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F90" s="7">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="G90" s="7">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="H90" s="10">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -4202,155 +4239,155 @@
         <v>214</v>
       </c>
       <c r="B91" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C91" t="s">
-        <v>53</v>
+        <v>213</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="E91" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F91" s="7">
-        <v>1</v>
+        <v>2.46</v>
       </c>
       <c r="G91" s="7">
-        <v>0.64</v>
+        <v>1.86</v>
       </c>
       <c r="H91" s="10">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>216</v>
+      </c>
+      <c r="B92" t="s">
+        <v>211</v>
+      </c>
+      <c r="C92" t="s">
         <v>215</v>
       </c>
-      <c r="B92" t="s">
-        <v>212</v>
-      </c>
-      <c r="C92" t="s">
-        <v>137</v>
-      </c>
       <c r="D92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E92" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F92" s="7">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="G92" s="7">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H92" s="10">
-        <v>12</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>218</v>
+      </c>
+      <c r="B93" t="s">
+        <v>211</v>
+      </c>
+      <c r="C93" t="s">
         <v>217</v>
       </c>
-      <c r="B93" t="s">
-        <v>212</v>
-      </c>
-      <c r="C93" t="s">
-        <v>216</v>
-      </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F93" s="7">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="G93" s="7">
-        <v>4.64</v>
+        <v>1.14</v>
       </c>
       <c r="H93" s="10">
-        <v>6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>220</v>
+      </c>
+      <c r="B94" t="s">
+        <v>211</v>
+      </c>
+      <c r="C94" t="s">
         <v>219</v>
       </c>
-      <c r="B94" t="s">
-        <v>212</v>
-      </c>
-      <c r="C94" t="s">
-        <v>218</v>
-      </c>
       <c r="D94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E94" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F94" s="7">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="G94" s="7">
-        <v>0.75</v>
+        <v>2.81</v>
       </c>
       <c r="H94" s="10">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>222</v>
+      </c>
+      <c r="B95" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" t="s">
         <v>221</v>
       </c>
-      <c r="B95" t="s">
-        <v>212</v>
-      </c>
-      <c r="C95" t="s">
-        <v>220</v>
-      </c>
       <c r="D95" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E95" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F95" s="7">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="G95" s="7">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="H95" s="10">
-        <v>11</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>224</v>
+      </c>
+      <c r="B96" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" t="s">
         <v>223</v>
       </c>
-      <c r="B96" t="s">
-        <v>224</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>225</v>
       </c>
-      <c r="D96" t="s">
-        <v>196</v>
-      </c>
       <c r="E96" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F96" s="7">
-        <v>0.9399999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="G96" s="7">
-        <v>0.89</v>
+        <v>2.01</v>
       </c>
       <c r="H96" s="10">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -4358,1712 +4395,1712 @@
         <v>226</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C97" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="E97" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F97" s="7">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="G97" s="7">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="H97" s="10">
-        <v>6.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>229</v>
+      </c>
+      <c r="B98" t="s">
         <v>227</v>
       </c>
-      <c r="B98" t="s">
-        <v>224</v>
-      </c>
       <c r="C98" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E98" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F98" s="7">
-        <v>2.62</v>
+        <v>4.68</v>
       </c>
       <c r="G98" s="7">
-        <v>2.7</v>
+        <v>1.22</v>
       </c>
       <c r="H98" s="10">
-        <v>11.7</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B99" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C99" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D99" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E99" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F99" s="7">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="G99" s="7">
-        <v>2.15</v>
+        <v>1.21</v>
       </c>
       <c r="H99" s="10">
-        <v>11.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B100" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D100" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="E100" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F100" s="7">
-        <v>2.08</v>
+        <v>3.84</v>
       </c>
       <c r="G100" s="7">
-        <v>3.26</v>
+        <v>1.19</v>
       </c>
       <c r="H100" s="10">
-        <v>8.6</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C101" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="D101" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F101" s="7">
-        <v>1.78</v>
+        <v>3.72</v>
       </c>
       <c r="G101" s="7">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="H101" s="10">
-        <v>9.199999999999999</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="D102" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E102" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F102" s="7">
-        <v>0.9399999999999999</v>
+        <v>4.52</v>
       </c>
       <c r="G102" s="7">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="H102" s="10">
-        <v>4.8</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B103" t="s">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="C103" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="E103" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F103" s="7">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="G103" s="7">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="H103" s="10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B104" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C104" t="s">
-        <v>111</v>
+        <v>243</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E104" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F104" s="7">
-        <v>2.44</v>
+        <v>1.66</v>
       </c>
       <c r="G104" s="7">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="H104" s="10">
-        <v>13.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C105" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D105" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E105" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F105" s="7">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="G105" s="7">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="H105" s="10">
-        <v>14.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B106" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C106" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D106" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F106" s="7">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="G106" s="7">
-        <v>0.95</v>
+        <v>1.46</v>
       </c>
       <c r="H106" s="10">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B107" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C107" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="E107" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F107" s="7">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="G107" s="7">
-        <v>2.17</v>
+        <v>1.38</v>
       </c>
       <c r="H107" s="10">
-        <v>11.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C108" t="s">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="D108" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
       <c r="E108" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F108" s="7">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="G108" s="7">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="H108" s="10">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="C109" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
       <c r="D109" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="E109" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F109" s="7">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="G109" s="7">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="H109" s="10">
-        <v>13.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B110" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C110" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="D110" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="E110" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F110" s="7">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G110" s="7">
-        <v>3.01</v>
+        <v>2.06</v>
       </c>
       <c r="H110" s="10">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B111" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C111" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="E111" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F111" s="7">
-        <v>2.68</v>
+        <v>4.24</v>
       </c>
       <c r="G111" s="7">
-        <v>0.99</v>
+        <v>1.33</v>
       </c>
       <c r="H111" s="10">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B112" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C112" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="D112" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F112" s="7">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="G112" s="7">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="H112" s="10">
-        <v>9.199999999999999</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="D113" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E113" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F113" s="7">
-        <v>1.06</v>
+        <v>3.72</v>
       </c>
       <c r="G113" s="7">
-        <v>2.91</v>
+        <v>1.35</v>
       </c>
       <c r="H113" s="10">
-        <v>4.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>260</v>
+      </c>
+      <c r="B114" t="s">
         <v>253</v>
       </c>
-      <c r="B114" t="s">
-        <v>247</v>
-      </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D114" t="s">
+        <v>261</v>
+      </c>
+      <c r="E114" t="s">
         <v>254</v>
       </c>
-      <c r="E114" t="s">
-        <v>177</v>
-      </c>
       <c r="F114" s="7">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="G114" s="7">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="H114" s="10">
-        <v>9.5</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C115" t="s">
+        <v>261</v>
+      </c>
+      <c r="D115" t="s">
+        <v>263</v>
+      </c>
+      <c r="E115" t="s">
         <v>254</v>
       </c>
-      <c r="D115" t="s">
-        <v>81</v>
-      </c>
-      <c r="E115" t="s">
-        <v>177</v>
-      </c>
       <c r="F115" s="7">
-        <v>2.56</v>
+        <v>4.28</v>
       </c>
       <c r="G115" s="7">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="H115" s="10">
-        <v>14.7</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B116" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C116" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="D116" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="E116" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F116" s="7">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="G116" s="7">
-        <v>0.83</v>
+        <v>1.35</v>
       </c>
       <c r="H116" s="10">
-        <v>6.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E117" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F117" s="7">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="G117" s="7">
-        <v>0.91</v>
+        <v>2.08</v>
       </c>
       <c r="H117" s="10">
-        <v>14.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D118" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F118" s="7">
-        <v>0.9</v>
+        <v>4.08</v>
       </c>
       <c r="G118" s="7">
-        <v>0.6899999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="H118" s="10">
-        <v>5.2</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D119" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E119" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F119" s="7">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="G119" s="7">
-        <v>0.79</v>
+        <v>1.79</v>
       </c>
       <c r="H119" s="10">
-        <v>14.9</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D120" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="E120" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F120" s="7">
-        <v>2.42</v>
+        <v>4.28</v>
       </c>
       <c r="G120" s="7">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="H120" s="10">
-        <v>14.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C121" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="D121" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="E121" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F121" s="7">
-        <v>2.1</v>
+        <v>3.32</v>
       </c>
       <c r="G121" s="7">
-        <v>0.73</v>
+        <v>2.01</v>
       </c>
       <c r="H121" s="10">
-        <v>12.1</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="D122" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="E122" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="F122" s="7">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="G122" s="7">
-        <v>0.76</v>
+        <v>1.96</v>
       </c>
       <c r="H122" s="10">
-        <v>13.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B123" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C123" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D123" t="s">
-        <v>52</v>
+        <v>279</v>
       </c>
       <c r="E123" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F123" s="7">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="G123" s="7">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="H123" s="10">
-        <v>10.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B124" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C124" t="s">
-        <v>52</v>
+        <v>279</v>
       </c>
       <c r="D124" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E124" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F124" s="7">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="G124" s="7">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="H124" s="10">
-        <v>10.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B125" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C125" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D125" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="E125" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F125" s="7">
-        <v>0.9399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="G125" s="7">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="H125" s="10">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>284</v>
+      </c>
+      <c r="B126" t="s">
         <v>276</v>
       </c>
-      <c r="B126" t="s">
-        <v>270</v>
-      </c>
       <c r="C126" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="D126" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E126" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F126" s="7">
-        <v>1.72</v>
+        <v>0.98</v>
       </c>
       <c r="G126" s="7">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="H126" s="10">
-        <v>9.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C127" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D127" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="E127" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F127" s="7">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="G127" s="7">
-        <v>0.87</v>
+        <v>1.76</v>
       </c>
       <c r="H127" s="10">
-        <v>11</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C128" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="D128" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E128" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F128" s="7">
-        <v>2.56</v>
+        <v>1</v>
       </c>
       <c r="G128" s="7">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="H128" s="10">
-        <v>12.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B129" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C129" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D129" t="s">
-        <v>284</v>
+        <v>201</v>
       </c>
       <c r="E129" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F129" s="7">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="G129" s="7">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="H129" s="10">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B130" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C130" t="s">
-        <v>284</v>
+        <v>140</v>
       </c>
       <c r="D130" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="E130" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F130" s="7">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="G130" s="7">
-        <v>0.73</v>
+        <v>2.54</v>
       </c>
       <c r="H130" s="10">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B131" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E131" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F131" s="7">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="G131" s="7">
-        <v>2.29</v>
+        <v>1.23</v>
       </c>
       <c r="H131" s="10">
-        <v>9.800000000000001</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B132" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D132" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E132" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F132" s="7">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="G132" s="7">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="H132" s="10">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B133" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D133" t="s">
-        <v>65</v>
+        <v>294</v>
       </c>
       <c r="E133" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F133" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="G133" s="7">
         <v>1.32</v>
       </c>
-      <c r="G133" s="7">
-        <v>1.65</v>
-      </c>
       <c r="H133" s="10">
-        <v>6.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B134" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>65</v>
+        <v>294</v>
       </c>
       <c r="D134" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="E134" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F134" s="7">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="G134" s="7">
-        <v>3.33</v>
+        <v>1.88</v>
       </c>
       <c r="H134" s="10">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B135" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="C135" t="s">
-        <v>292</v>
+        <v>86</v>
       </c>
       <c r="D135" t="s">
-        <v>47</v>
+        <v>297</v>
       </c>
       <c r="E135" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F135" s="7">
-        <v>1</v>
+        <v>2.42</v>
       </c>
       <c r="G135" s="7">
-        <v>0.84</v>
+        <v>1.45</v>
       </c>
       <c r="H135" s="10">
-        <v>5.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="C136" t="s">
-        <v>47</v>
+        <v>297</v>
       </c>
       <c r="D136" t="s">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="E136" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F136" s="7">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="G136" s="7">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="H136" s="10">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B137" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="C137" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D137" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="E137" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F137" s="7">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="G137" s="7">
-        <v>0.29</v>
+        <v>1.78</v>
       </c>
       <c r="H137" s="10">
-        <v>15.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="C138" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="D138" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="E138" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F138" s="7">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G138" s="7">
-        <v>0.92</v>
+        <v>1.73</v>
       </c>
       <c r="H138" s="10">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="C139" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="D139" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="E139" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F139" s="7">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="G139" s="7">
-        <v>0.9399999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="H139" s="10">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B140" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="C140" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="D140" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E140" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F140" s="7">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="G140" s="7">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="H140" s="10">
-        <v>8.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B141" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="C141" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D141" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
       <c r="E141" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F141" s="7">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G141" s="7">
-        <v>2.82</v>
+        <v>2.05</v>
       </c>
       <c r="H141" s="10">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B142" t="s">
-        <v>127</v>
+        <v>300</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D142" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F142" s="7">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="G142" s="7">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="H142" s="10">
-        <v>6.9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C143" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="D143" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E143" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F143" s="7">
-        <v>1.18</v>
+        <v>4.04</v>
       </c>
       <c r="G143" s="7">
-        <v>0.82</v>
+        <v>1.19</v>
       </c>
       <c r="H143" s="10">
-        <v>6.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B144" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C144" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D144" t="s">
-        <v>132</v>
+        <v>313</v>
       </c>
       <c r="E144" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F144" s="7">
-        <v>1.62</v>
+        <v>3.16</v>
       </c>
       <c r="G144" s="7">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="H144" s="10">
-        <v>7.4</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B145" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C145" t="s">
-        <v>132</v>
+        <v>313</v>
       </c>
       <c r="D145" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="E145" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F145" s="7">
-        <v>1.68</v>
+        <v>3.52</v>
       </c>
       <c r="G145" s="7">
-        <v>0.9</v>
+        <v>1.92</v>
       </c>
       <c r="H145" s="10">
-        <v>9.5</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B146" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C146" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="D146" t="s">
-        <v>309</v>
+        <v>238</v>
       </c>
       <c r="E146" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F146" s="7">
-        <v>1.44</v>
+        <v>3.96</v>
       </c>
       <c r="G146" s="7">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="H146" s="10">
-        <v>7.3</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>316</v>
+      </c>
+      <c r="B147" t="s">
         <v>310</v>
       </c>
-      <c r="B147" t="s">
-        <v>127</v>
-      </c>
       <c r="C147" t="s">
-        <v>309</v>
+        <v>238</v>
       </c>
       <c r="D147" t="s">
-        <v>311</v>
+        <v>223</v>
       </c>
       <c r="E147" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F147" s="7">
-        <v>1.44</v>
+        <v>3.68</v>
       </c>
       <c r="G147" s="7">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="H147" s="10">
-        <v>7.4</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B148" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C148" t="s">
-        <v>311</v>
+        <v>223</v>
       </c>
       <c r="D148" t="s">
-        <v>31</v>
+        <v>318</v>
       </c>
       <c r="E148" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F148" s="7">
-        <v>1.94</v>
+        <v>4.56</v>
       </c>
       <c r="G148" s="7">
-        <v>3.38</v>
+        <v>1.24</v>
       </c>
       <c r="H148" s="10">
-        <v>7.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B149" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C149" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D149" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="E149" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F149" s="7">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="G149" s="7">
-        <v>0.71</v>
+        <v>1.87</v>
       </c>
       <c r="H149" s="10">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B150" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C150" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="D150" t="s">
-        <v>260</v>
+        <v>323</v>
       </c>
       <c r="E150" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F150" s="7">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="G150" s="7">
-        <v>0.6</v>
+        <v>2.93</v>
       </c>
       <c r="H150" s="10">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B151" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C151" t="s">
-        <v>260</v>
+        <v>323</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E151" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F151" s="7">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="G151" s="7">
-        <v>0.85</v>
+        <v>2.01</v>
       </c>
       <c r="H151" s="10">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B152" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C152" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D152" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="E152" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F152" s="7">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="G152" s="7">
-        <v>0.68</v>
+        <v>1.34</v>
       </c>
       <c r="H152" s="10">
-        <v>15.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B153" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C153" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="D153" t="s">
-        <v>75</v>
+        <v>328</v>
       </c>
       <c r="E153" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F153" s="7">
-        <v>0.98</v>
+        <v>1.76</v>
       </c>
       <c r="G153" s="7">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="H153" s="10">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B154" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="C154" t="s">
-        <v>75</v>
+        <v>328</v>
       </c>
       <c r="D154" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="E154" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="F154" s="7">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="G154" s="7">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H154" s="10">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B155" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C155" t="s">
-        <v>123</v>
+        <v>331</v>
       </c>
       <c r="D155" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="E155" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F155" s="7">
-        <v>1.14</v>
+        <v>2.46</v>
       </c>
       <c r="G155" s="7">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="H155" s="10">
-        <v>5.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B156" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C156" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="D156" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="E156" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F156" s="7">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="G156" s="7">
-        <v>0.78</v>
+        <v>1.29</v>
       </c>
       <c r="H156" s="10">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B157" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C157" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="D157" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
       <c r="E157" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F157" s="7">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="G157" s="7">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="H157" s="10">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B158" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C158" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
       <c r="D158" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="E158" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F158" s="7">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="G158" s="7">
-        <v>3.01</v>
+        <v>1.71</v>
       </c>
       <c r="H158" s="10">
-        <v>5.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B159" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C159" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E159" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F159" s="7">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="G159" s="7">
-        <v>0.54</v>
+        <v>1.25</v>
       </c>
       <c r="H159" s="10">
-        <v>6.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C160" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D160" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="E160" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F160" s="7">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="G160" s="7">
-        <v>3.4</v>
+        <v>1.31</v>
       </c>
       <c r="H160" s="10">
-        <v>9.699999999999999</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B161" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C161" t="s">
-        <v>125</v>
+        <v>343</v>
       </c>
       <c r="D161" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="E161" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F161" s="7">
-        <v>1.82</v>
+        <v>2.48</v>
       </c>
       <c r="G161" s="7">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H161" s="10">
-        <v>9.800000000000001</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B162" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C162" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="D162" t="s">
-        <v>176</v>
+        <v>346</v>
       </c>
       <c r="E162" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F162" s="7">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="G162" s="7">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="H162" s="10">
         <v>8.800000000000001</v>
@@ -6071,1221 +6108,1221 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B163" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C163" t="s">
-        <v>176</v>
+        <v>346</v>
       </c>
       <c r="D163" t="s">
-        <v>336</v>
+        <v>88</v>
       </c>
       <c r="E163" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F163" s="7">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="G163" s="7">
-        <v>0.65</v>
+        <v>1.86</v>
       </c>
       <c r="H163" s="10">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B164" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C164" t="s">
-        <v>336</v>
+        <v>88</v>
       </c>
       <c r="D164" t="s">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="E164" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F164" s="7">
-        <v>0.96</v>
+        <v>2.12</v>
       </c>
       <c r="G164" s="7">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="H164" s="10">
-        <v>4.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B165" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="D165" t="s">
-        <v>339</v>
+        <v>122</v>
       </c>
       <c r="E165" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F165" s="7">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="G165" s="7">
-        <v>1.79</v>
+        <v>2.43</v>
       </c>
       <c r="H165" s="10">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B166" t="s">
-        <v>73</v>
+        <v>342</v>
       </c>
       <c r="C166" t="s">
-        <v>339</v>
+        <v>122</v>
       </c>
       <c r="D166" t="s">
-        <v>341</v>
+        <v>215</v>
       </c>
       <c r="E166" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F166" s="7">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="G166" s="7">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="H166" s="10">
-        <v>12.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B167" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C167" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="D167" t="s">
+        <v>353</v>
+      </c>
+      <c r="E167" t="s">
         <v>344</v>
       </c>
-      <c r="E167" t="s">
-        <v>324</v>
-      </c>
       <c r="F167" s="7">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="G167" s="7">
-        <v>3.74</v>
+        <v>1.56</v>
       </c>
       <c r="H167" s="10">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B168" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C168" t="s">
+        <v>353</v>
+      </c>
+      <c r="D168" t="s">
+        <v>355</v>
+      </c>
+      <c r="E168" t="s">
         <v>344</v>
       </c>
-      <c r="D168" t="s">
-        <v>346</v>
-      </c>
-      <c r="E168" t="s">
-        <v>324</v>
-      </c>
       <c r="F168" s="7">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="G168" s="7">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="H168" s="10">
-        <v>6.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B169" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C169" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D169" t="s">
-        <v>348</v>
+        <v>191</v>
       </c>
       <c r="E169" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F169" s="7">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="G169" s="7">
-        <v>2.58</v>
+        <v>1.54</v>
       </c>
       <c r="H169" s="10">
-        <v>5.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B170" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C170" t="s">
-        <v>348</v>
+        <v>191</v>
       </c>
       <c r="D170" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="E170" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F170" s="7">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="G170" s="7">
-        <v>0.89</v>
+        <v>1.73</v>
       </c>
       <c r="H170" s="10">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B171" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C171" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="D171" t="s">
-        <v>123</v>
+        <v>360</v>
       </c>
       <c r="E171" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F171" s="7">
-        <v>1.8</v>
+        <v>0.86</v>
       </c>
       <c r="G171" s="7">
-        <v>1.19</v>
+        <v>3.11</v>
       </c>
       <c r="H171" s="10">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B172" t="s">
-        <v>259</v>
+        <v>352</v>
       </c>
       <c r="C172" t="s">
-        <v>123</v>
+        <v>360</v>
       </c>
       <c r="D172" t="s">
-        <v>352</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F172" s="7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G172" s="7">
-        <v>0.28</v>
+        <v>1.24</v>
       </c>
       <c r="H172" s="10">
-        <v>13</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B173" t="s">
-        <v>225</v>
+        <v>352</v>
       </c>
       <c r="C173" t="s">
-        <v>354</v>
+        <v>134</v>
       </c>
       <c r="D173" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="E173" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F173" s="7">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="G173" s="7">
-        <v>0.36</v>
+        <v>2.1</v>
       </c>
       <c r="H173" s="10">
-        <v>12.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B174" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="E174" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F174" s="7">
-        <v>3.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G174" s="7">
-        <v>1.4</v>
+        <v>2.54</v>
       </c>
       <c r="H174" s="10">
-        <v>20.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B175" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C175" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="D175" t="s">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="E175" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F175" s="7">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="G175" s="7">
-        <v>3.89</v>
+        <v>1.93</v>
       </c>
       <c r="H175" s="10">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B176" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C176" t="s">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="D176" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="E176" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F176" s="7">
-        <v>4.32</v>
+        <v>0.86</v>
       </c>
       <c r="G176" s="7">
-        <v>1.95</v>
+        <v>3.04</v>
       </c>
       <c r="H176" s="10">
-        <v>21.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B177" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C177" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="D177" t="s">
-        <v>99</v>
+        <v>369</v>
       </c>
       <c r="E177" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F177" s="7">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="G177" s="7">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="H177" s="10">
-        <v>14.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B178" t="s">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="C178" t="s">
-        <v>99</v>
+        <v>369</v>
       </c>
       <c r="D178" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E178" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F178" s="7">
-        <v>4.84</v>
+        <v>1.84</v>
       </c>
       <c r="G178" s="7">
-        <v>2.34</v>
+        <v>1.18</v>
       </c>
       <c r="H178" s="10">
-        <v>22.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B179" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C179" t="s">
-        <v>113</v>
+        <v>371</v>
       </c>
       <c r="D179" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="E179" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F179" s="7">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="G179" s="7">
-        <v>0.63</v>
+        <v>2.39</v>
       </c>
       <c r="H179" s="10">
-        <v>12.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C180" t="s">
-        <v>136</v>
+        <v>375</v>
       </c>
       <c r="D180" t="s">
+        <v>223</v>
+      </c>
+      <c r="E180" t="s">
         <v>344</v>
       </c>
-      <c r="E180" t="s">
-        <v>324</v>
-      </c>
       <c r="F180" s="7">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="G180" s="7">
-        <v>2.37</v>
+        <v>1.08</v>
       </c>
       <c r="H180" s="10">
-        <v>9.300000000000001</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B181" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C181" t="s">
+        <v>223</v>
+      </c>
+      <c r="D181" t="s">
+        <v>377</v>
+      </c>
+      <c r="E181" t="s">
         <v>344</v>
       </c>
-      <c r="D181" t="s">
-        <v>216</v>
-      </c>
-      <c r="E181" t="s">
-        <v>324</v>
-      </c>
       <c r="F181" s="7">
-        <v>2.12</v>
+        <v>1.14</v>
       </c>
       <c r="G181" s="7">
-        <v>0.59</v>
+        <v>1.87</v>
       </c>
       <c r="H181" s="10">
-        <v>12.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B182" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="D182" t="s">
-        <v>161</v>
+        <v>379</v>
       </c>
       <c r="E182" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F182" s="7">
-        <v>2.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G182" s="7">
-        <v>1.42</v>
+        <v>2.42</v>
       </c>
       <c r="H182" s="10">
-        <v>10.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B183" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C183" t="s">
-        <v>161</v>
+        <v>379</v>
       </c>
       <c r="D183" t="s">
-        <v>37</v>
+        <v>381</v>
       </c>
       <c r="E183" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F183" s="7">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="G183" s="7">
-        <v>0.73</v>
+        <v>1.37</v>
       </c>
       <c r="H183" s="10">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B184" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C184" t="s">
-        <v>37</v>
+        <v>381</v>
       </c>
       <c r="D184" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="E184" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F184" s="7">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="G184" s="7">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="H184" s="10">
-        <v>16.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C185" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="D185" t="s">
-        <v>247</v>
+        <v>39</v>
       </c>
       <c r="E185" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F185" s="7">
-        <v>2.64</v>
+        <v>1.64</v>
       </c>
       <c r="G185" s="7">
-        <v>0.9</v>
+        <v>1.34</v>
       </c>
       <c r="H185" s="10">
-        <v>14.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C186" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="D186" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E186" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F186" s="7">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G186" s="7">
-        <v>0.93</v>
+        <v>1.97</v>
       </c>
       <c r="H186" s="10">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C187" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D187" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="E187" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F187" s="7">
-        <v>1.9</v>
+        <v>0.98</v>
       </c>
       <c r="G187" s="7">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="H187" s="10">
-        <v>9.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B188" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C188" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="D188" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="E188" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F188" s="7">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="G188" s="7">
-        <v>3.01</v>
+        <v>2.01</v>
       </c>
       <c r="H188" s="10">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B189" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C189" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="D189" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E189" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F189" s="7">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="G189" s="7">
-        <v>0.9399999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="H189" s="10">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B190" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C190" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="D190" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E190" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F190" s="7">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="G190" s="7">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="H190" s="10">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B191" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C191" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D191" t="s">
-        <v>381</v>
+        <v>223</v>
       </c>
       <c r="E191" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F191" s="7">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="G191" s="7">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="H191" s="10">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B192" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C192" t="s">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="D192" t="s">
-        <v>384</v>
+        <v>263</v>
       </c>
       <c r="E192" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F192" s="7">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="G192" s="7">
-        <v>3.72</v>
+        <v>1.65</v>
       </c>
       <c r="H192" s="10">
-        <v>9.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B193" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C193" t="s">
-        <v>384</v>
+        <v>263</v>
       </c>
       <c r="D193" t="s">
-        <v>153</v>
+        <v>396</v>
       </c>
       <c r="E193" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F193" s="7">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="G193" s="7">
-        <v>2.19</v>
+        <v>1.11</v>
       </c>
       <c r="H193" s="10">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B194" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C194" t="s">
-        <v>153</v>
+        <v>396</v>
       </c>
       <c r="D194" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E194" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F194" s="7">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="G194" s="7">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="H194" s="10">
-        <v>7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B195" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C195" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D195" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E195" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F195" s="7">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="G195" s="7">
-        <v>1.04</v>
+        <v>2.09</v>
       </c>
       <c r="H195" s="10">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B196" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C196" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D196" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="E196" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F196" s="7">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G196" s="7">
-        <v>2.16</v>
+        <v>1.05</v>
       </c>
       <c r="H196" s="10">
-        <v>7.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C197" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="D197" t="s">
-        <v>218</v>
+        <v>375</v>
       </c>
       <c r="E197" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F197" s="7">
-        <v>0.96</v>
+        <v>1.74</v>
       </c>
       <c r="G197" s="7">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="H197" s="10">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B198" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C198" t="s">
-        <v>218</v>
+        <v>375</v>
       </c>
       <c r="D198" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="E198" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F198" s="7">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="G198" s="7">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="H198" s="10">
-        <v>12.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B199" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C199" t="s">
-        <v>305</v>
+        <v>124</v>
       </c>
       <c r="D199" t="s">
-        <v>395</v>
+        <v>120</v>
       </c>
       <c r="E199" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F199" s="7">
-        <v>5.24</v>
+        <v>2.16</v>
       </c>
       <c r="G199" s="7">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="H199" s="10">
-        <v>27.6</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B200" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C200" t="s">
-        <v>395</v>
+        <v>120</v>
       </c>
       <c r="D200" t="s">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="E200" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F200" s="7">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G200" s="7">
-        <v>2.11</v>
+        <v>1.45</v>
       </c>
       <c r="H200" s="10">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B201" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C201" t="s">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="D201" t="s">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="E201" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F201" s="7">
-        <v>4.48</v>
+        <v>1.64</v>
       </c>
       <c r="G201" s="7">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="H201" s="10">
-        <v>24.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B202" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C202" t="s">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="D202" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E202" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F202" s="7">
-        <v>4.24</v>
+        <v>1.4</v>
       </c>
       <c r="G202" s="7">
-        <v>1.59</v>
+        <v>2.87</v>
       </c>
       <c r="H202" s="10">
-        <v>22.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C203" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="D203" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="E203" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F203" s="7">
-        <v>4.76</v>
+        <v>2.36</v>
       </c>
       <c r="G203" s="7">
-        <v>1.86</v>
+        <v>1.09</v>
       </c>
       <c r="H203" s="10">
-        <v>23.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B204" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C204" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="D204" t="s">
-        <v>336</v>
+        <v>415</v>
       </c>
       <c r="E204" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F204" s="7">
-        <v>5.24</v>
+        <v>1.88</v>
       </c>
       <c r="G204" s="7">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="H204" s="10">
-        <v>25.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>213</v>
+        <v>417</v>
       </c>
       <c r="C205" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="D205" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="E205" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F205" s="7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G205" s="7">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="H205" s="10">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="B206" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C206" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="D206" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="E206" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F206" s="7">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="G206" s="7">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="H206" s="10">
-        <v>9.699999999999999</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C207" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="D207" t="s">
-        <v>407</v>
+        <v>62</v>
       </c>
       <c r="E207" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F207" s="7">
-        <v>1.62</v>
+        <v>0.86</v>
       </c>
       <c r="G207" s="7">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="H207" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B208" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C208" t="s">
-        <v>407</v>
+        <v>62</v>
       </c>
       <c r="D208" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="E208" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F208" s="7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G208" s="7">
-        <v>0.6899999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="H208" s="10">
-        <v>8.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="B209" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="D209" t="s">
-        <v>206</v>
+        <v>423</v>
       </c>
       <c r="E209" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F209" s="7">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="G209" s="7">
-        <v>2.77</v>
+        <v>1.17</v>
       </c>
       <c r="H209" s="10">
         <v>11.4</v>
@@ -7293,221 +7330,221 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C210" t="s">
-        <v>206</v>
+        <v>423</v>
       </c>
       <c r="D210" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E210" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F210" s="7">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="G210" s="7">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="H210" s="10">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B211" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D211" t="s">
-        <v>224</v>
+        <v>24</v>
       </c>
       <c r="E211" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F211" s="7">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="G211" s="7">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="H211" s="10">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B212" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C212" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="D212" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="E212" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F212" s="7">
-        <v>2.2</v>
+        <v>0.96</v>
       </c>
       <c r="G212" s="7">
-        <v>1.56</v>
+        <v>3.04</v>
       </c>
       <c r="H212" s="10">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B213" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C213" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="D213" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="E213" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F213" s="7">
-        <v>1.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G213" s="7">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="H213" s="10">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B214" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C214" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="D214" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="E214" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F214" s="7">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="G214" s="7">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="10">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B215" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C215" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D215" t="s">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="E215" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F215" s="7">
-        <v>0.98</v>
+        <v>1.76</v>
       </c>
       <c r="G215" s="7">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="H215" s="10">
-        <v>5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B216" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C216" t="s">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="D216" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="E216" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F216" s="7">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G216" s="7">
-        <v>1.24</v>
+        <v>2.91</v>
       </c>
       <c r="H216" s="10">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B217" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="C217" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="D217" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E217" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F217" s="7">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G217" s="7">
-        <v>0.43</v>
+        <v>1.44</v>
       </c>
       <c r="H217" s="10">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F218" s="11">
         <v>424</v>
       </c>
       <c r="H218" s="12">
-        <v>2204.5</v>
+        <v>2202.6</v>
       </c>
     </row>
   </sheetData>
@@ -7532,15 +7569,15 @@
         <v>17</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B2" s="13">
         <v>7843.2</v>
@@ -7551,7 +7588,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B3" s="13">
         <v>7142.4</v>
@@ -7562,7 +7599,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B4" s="13">
         <v>8447.4</v>
@@ -7573,7 +7610,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B5" s="13">
         <v>6279.6</v>
@@ -7584,7 +7621,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -7608,74 +7645,74 @@
         <v>17</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="13">
-        <v>4487.3</v>
-      </c>
-      <c r="C2" s="13">
-        <v>7883.9</v>
-      </c>
-      <c r="D2" s="13">
-        <v>6158.2</v>
+        <v>438</v>
+      </c>
+      <c r="B2" s="14">
+        <v>5488</v>
+      </c>
+      <c r="C2" s="14">
+        <v>9645</v>
+      </c>
+      <c r="D2" s="14">
+        <v>8215</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>427</v>
-      </c>
-      <c r="B3" s="13">
-        <v>5663.7</v>
-      </c>
-      <c r="C3" s="13">
-        <v>9845.299999999999</v>
-      </c>
-      <c r="D3" s="13">
-        <v>7701.5</v>
+        <v>439</v>
+      </c>
+      <c r="B3" s="14">
+        <v>7566</v>
+      </c>
+      <c r="C3" s="14">
+        <v>13174</v>
+      </c>
+      <c r="D3" s="14">
+        <v>11467</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>428</v>
-      </c>
-      <c r="B4" s="13">
-        <v>5050.2</v>
-      </c>
-      <c r="C4" s="13">
-        <v>8836.6</v>
-      </c>
-      <c r="D4" s="13">
-        <v>6896.9</v>
+        <v>440</v>
+      </c>
+      <c r="B4" s="14">
+        <v>7224</v>
+      </c>
+      <c r="C4" s="14">
+        <v>12617</v>
+      </c>
+      <c r="D4" s="14">
+        <v>10808</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>429</v>
-      </c>
-      <c r="B5" s="13">
-        <v>7519.9</v>
-      </c>
-      <c r="C5" s="13">
-        <v>13243.7</v>
-      </c>
-      <c r="D5" s="13">
-        <v>10252.3</v>
+        <v>441</v>
+      </c>
+      <c r="B5" s="14">
+        <v>3005</v>
+      </c>
+      <c r="C5" s="14">
+        <v>5193</v>
+      </c>
+      <c r="D5" s="14">
+        <v>4543</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7692,38 +7729,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>435</v>
+      <c r="A1" s="15" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>436</v>
+      <c r="A2" s="15" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>437</v>
+      <c r="A3" s="15" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>438</v>
+      <c r="A4" s="15" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>439</v>
+      <c r="A5" s="15" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>440</v>
+      <c r="A6" s="15" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>441</v>
+      <c r="A7" s="15" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/task165/golden/salt_commitment_2026-27.xlsx
+++ b/task165/golden/salt_commitment_2026-27.xlsx
@@ -1385,10 +1385,10 @@
     <t>Collector figures are rock salt (RS) only; the collector and local circuits spread dry salt.</t>
   </si>
   <si>
-    <t>Dome stock: survey report TG-2026-0917 brought forward by the scale house weighings after each capture, loads weighed at another yard's scale counted at the dome named in the remarks, and the 21 September dispatch issue.</t>
-  </si>
-  <si>
-    <t>Arterial salt: older-controller runs counted once with the spinner brine taken off at 1.18 kg a litre; Kettlewood Road Services circuits from its monthly returns; each circuit under the yard that ran it that winter.</t>
+    <t>Dome stock: survey report TG-2026-0917 brought forward by the scale house weighings after each capture, loads weighed at another yard's scale counted at the dome named in the remarks, the five supplier loads weighed again at another yard's scale on their way to their own yard (the same truck on the same gross, back at a City scale inside its round trip from the supplier) counted once, on their own yard's ticket (RO-PR-07 section 2: deliveries weighed at the yard's scale house), and the BOOKED October loads of the 21 September dispatch issue.</t>
+  </si>
+  <si>
+    <t>Arterial salt: the M410 spreader controllers' runs (up to each unit's replacement in Fleet Services' work orders), which carry one total of salt and brine on every row, counted once with the spinner brine taken off at 1.18 kg a litre; Kettlewood Road Services circuits from its monthly returns; each circuit under the yard it belonged to that winter, the platform's current circuit codes taken back through the route audit's 1 July 2026 changes.</t>
   </si>
 </sst>
 </file>
